--- a/Output/FEATURES.xlsx
+++ b/Output/FEATURES.xlsx
@@ -446,3098 +446,3098 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-11.34978828875349</v>
+        <v>-4.376514947481821</v>
       </c>
       <c r="C2" t="n">
-        <v>106.28</v>
+        <v>18.6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8038210624417521</v>
+        <v>1.133643148852274</v>
       </c>
       <c r="E2" t="n">
-        <v>1.637359832370646</v>
+        <v>1.007064223020927</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-7.861994754186568</v>
+        <v>0.8458723058153795</v>
       </c>
       <c r="C3" t="n">
-        <v>60.3</v>
+        <v>15.44</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.510948905109496</v>
+        <v>4.822969594322118</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>1.363086982849553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.689266197141941</v>
+        <v>1.712439418416801</v>
       </c>
       <c r="C4" t="n">
-        <v>36.13</v>
+        <v>14.3</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.102411525211394</v>
+        <v>-0.8386277001270678</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1775776369663375</v>
+        <v>1.314779319842169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7932446264073754</v>
+        <v>-2.000367039823817</v>
       </c>
       <c r="C5" t="n">
-        <v>34.22</v>
+        <v>13.53</v>
       </c>
       <c r="D5" t="n">
-        <v>1.096208408563322</v>
+        <v>0.7490636704119851</v>
       </c>
       <c r="E5" t="n">
-        <v>3.145071456602396</v>
+        <v>0.5732511785235249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0124115675809883</v>
+        <v>0.6081964417666144</v>
       </c>
       <c r="C6" t="n">
-        <v>31.14</v>
+        <v>12.89</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.68818272095333</v>
+        <v>2.192090395480224</v>
       </c>
       <c r="E6" t="n">
-        <v>1.253577075513076</v>
+        <v>0.5022414736101887</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.879501141753035</v>
+        <v>-1.262714836899341</v>
       </c>
       <c r="C7" t="n">
-        <v>31.14</v>
+        <v>11.64</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2931034482758568</v>
+        <v>0.9378330373001728</v>
       </c>
       <c r="E7" t="n">
-        <v>14.08015116784136</v>
+        <v>2.924939934367309</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.429000429000429</v>
+        <v>0.3751131807010706</v>
       </c>
       <c r="C8" t="n">
-        <v>28.08</v>
+        <v>11.43</v>
       </c>
       <c r="D8" t="n">
-        <v>0.341734301580526</v>
+        <v>0.618556701030922</v>
       </c>
       <c r="E8" t="n">
-        <v>10.14315015080433</v>
+        <v>1.564908322589887</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.8698132040496092</v>
+        <v>0.08621928437994292</v>
       </c>
       <c r="C9" t="n">
-        <v>27.62</v>
+        <v>11.34</v>
       </c>
       <c r="D9" t="n">
-        <v>1.071634062140381</v>
+        <v>1.019382627422819</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9054707464542343</v>
+        <v>7.73744441080335</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.53802840574838</v>
+        <v>5.51744706233224</v>
       </c>
       <c r="C10" t="n">
-        <v>27.07</v>
+        <v>10.87</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5288724095312033</v>
+        <v>1.985585076314302</v>
       </c>
       <c r="E10" t="n">
-        <v>1.086779818780081</v>
+        <v>0.6150684162206509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.536022945993879</v>
+        <v>1.22991469946439</v>
       </c>
       <c r="C11" t="n">
-        <v>26.86</v>
+        <v>10.87</v>
       </c>
       <c r="D11" t="n">
-        <v>1.694135684170173</v>
+        <v>1.616696061140495</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4281850598772922</v>
+        <v>1.514841827167246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.258422806368012</v>
+        <v>-0.08888888888888889</v>
       </c>
       <c r="C12" t="n">
-        <v>26.49</v>
+        <v>10.72</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.730629978276618</v>
+        <v>-0.03558718861210773</v>
       </c>
       <c r="E12" t="n">
-        <v>2.350146505868858</v>
+        <v>1.365947018530817</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.521791823987316</v>
+        <v>-3.576563623292591</v>
       </c>
       <c r="C13" t="n">
-        <v>26.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.509775393289091</v>
+        <v>2.087604846225545</v>
       </c>
       <c r="E13" t="n">
-        <v>1.991474188937513</v>
+        <v>2.21008361982524</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.929384965831435</v>
+        <v>0.5779650812763341</v>
       </c>
       <c r="C14" t="n">
-        <v>26.09</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8675799086757991</v>
+        <v>0.634502573925544</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4301952535972411</v>
+        <v>2.460246399317628</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9457441513190529</v>
+        <v>1.542971763616726</v>
       </c>
       <c r="C15" t="n">
-        <v>24.67</v>
+        <v>9.43</v>
       </c>
       <c r="D15" t="n">
-        <v>2.186061801446428</v>
+        <v>0.7445676948791942</v>
       </c>
       <c r="E15" t="n">
-        <v>7.597494528086062</v>
+        <v>6.337324686486697</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.93398533007335</v>
+        <v>-1.169590643274846</v>
       </c>
       <c r="C16" t="n">
-        <v>24.6</v>
+        <v>9.32</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.18387909319899</v>
+        <v>1.427079707622682</v>
       </c>
       <c r="E16" t="n">
-        <v>9.873257763563965</v>
+        <v>7.398603026396322</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.281108894256016</v>
+        <v>-1.301538604564682</v>
       </c>
       <c r="C17" t="n">
-        <v>24.33</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>1.016070502851214</v>
+        <v>3.409786652851675</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1379521974022969</v>
+        <v>0.9621985323800967</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.09188953910142143</v>
+        <v>3.369334441059725</v>
       </c>
       <c r="C18" t="n">
-        <v>23.92</v>
+        <v>9.1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2174333204483959</v>
+        <v>-0.1786033220217896</v>
       </c>
       <c r="E18" t="n">
-        <v>2.710627625676245</v>
+        <v>0.1386523160266177</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.2539579618522746</v>
+        <v>-1.951247101408291</v>
       </c>
       <c r="C19" t="n">
-        <v>23.79</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3250270855904659</v>
+        <v>1.822796492847262</v>
       </c>
       <c r="E19" t="n">
-        <v>2.902822151719212</v>
+        <v>0.7430196084176531</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.372368362487212</v>
+        <v>2.719665271966528</v>
       </c>
       <c r="C20" t="n">
-        <v>23.73</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.804347826086956</v>
+        <v>3.065173116089615</v>
       </c>
       <c r="E20" t="n">
-        <v>1.089546753852893</v>
+        <v>0.417956694143845</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.158199526191103</v>
+        <v>-0.5206192629127215</v>
       </c>
       <c r="C21" t="n">
-        <v>23.64</v>
+        <v>8.58</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.812250332889481</v>
+        <v>2.299958683376936</v>
       </c>
       <c r="E21" t="n">
-        <v>0.617274080733052</v>
+        <v>4.208099337813025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9321323837452966</v>
+        <v>-0.5431619786614996</v>
       </c>
       <c r="C22" t="n">
-        <v>23.56</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7004254436027809</v>
+        <v>1.248293348937003</v>
       </c>
       <c r="E22" t="n">
-        <v>2.034422710094563</v>
+        <v>1.579850259144952</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-2.016285381930977</v>
+        <v>1.456844420010998</v>
       </c>
       <c r="C23" t="n">
-        <v>22.57</v>
+        <v>8.19</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6727344677483137</v>
+        <v>-1.35464643727987</v>
       </c>
       <c r="E23" t="n">
-        <v>23.80349348106594</v>
+        <v>1.64025406623172</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.588551047074202</v>
+        <v>-1.050048507675628</v>
       </c>
       <c r="C24" t="n">
-        <v>22.06</v>
+        <v>7.79</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.333907056798629</v>
+        <v>-2.45688909395005</v>
       </c>
       <c r="E24" t="n">
-        <v>2.332761620371095</v>
+        <v>6.038321548098084</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-2.726502963590182</v>
+        <v>-0.7677183784289691</v>
       </c>
       <c r="C25" t="n">
-        <v>21.7</v>
+        <v>7.51</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5571030640668405</v>
+        <v>-2.320973676761971</v>
       </c>
       <c r="E25" t="n">
-        <v>3.561883903883235</v>
+        <v>0.4322357112161582</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.5309281647796299</v>
+        <v>2.448061400026465</v>
       </c>
       <c r="C26" t="n">
-        <v>21.52</v>
+        <v>7.44</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3215434083601286</v>
+        <v>-0.8912425729785702</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3412614283997176</v>
+        <v>3.24571279511922</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5475628086751152</v>
+        <v>-0.456100342075245</v>
       </c>
       <c r="C27" t="n">
-        <v>20.86</v>
+        <v>7.38</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5605979711692471</v>
+        <v>-0.3309151075474128</v>
       </c>
       <c r="E27" t="n">
-        <v>0.439363445731005</v>
+        <v>2.806155669284161</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.300258207303575</v>
+        <v>-0.341779611078371</v>
       </c>
       <c r="C28" t="n">
-        <v>20.71</v>
+        <v>7.25</v>
       </c>
       <c r="D28" t="n">
-        <v>2.039144287665006</v>
+        <v>-0.2956480605487228</v>
       </c>
       <c r="E28" t="n">
-        <v>18.65098489144131</v>
+        <v>1.225934679845294</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.055942484834883</v>
+        <v>1.013790532985457</v>
       </c>
       <c r="C29" t="n">
-        <v>20.17</v>
+        <v>7.02</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.034183799851364</v>
+        <v>-0.4427717511622759</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8902435820930372</v>
+        <v>0.3841506491646157</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7201280227596139</v>
+        <v>0.8220502901353964</v>
       </c>
       <c r="C30" t="n">
-        <v>20.1</v>
+        <v>6.94</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7591137787977675</v>
+        <v>1.525179856115117</v>
       </c>
       <c r="E30" t="n">
-        <v>2.087435732042451</v>
+        <v>0.6082308636428748</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2007248396989077</v>
+        <v>-2.961319571717955</v>
       </c>
       <c r="C31" t="n">
-        <v>19.34</v>
+        <v>6.74</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.06704285155595538</v>
+        <v>-1.759443339960243</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1380777018412536</v>
+        <v>9.818966008386399</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.11154069205489</v>
+        <v>-3.387803905938627</v>
       </c>
       <c r="C32" t="n">
-        <v>19.32</v>
+        <v>6.51</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.280422246114751</v>
+        <v>1.980198019801982</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2078382696201514</v>
+        <v>65.23126611516975</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.770093839249293</v>
+        <v>0.3436847919479507</v>
       </c>
       <c r="C33" t="n">
-        <v>18.98</v>
+        <v>6.47</v>
       </c>
       <c r="D33" t="n">
-        <v>1.700490915532158</v>
+        <v>1.045871559633022</v>
       </c>
       <c r="E33" t="n">
-        <v>5.273776126083935</v>
+        <v>1.833522971441966</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6874522602597105</v>
+        <v>0.5235602094240838</v>
       </c>
       <c r="C34" t="n">
-        <v>18.7</v>
+        <v>6.39</v>
       </c>
       <c r="D34" t="n">
-        <v>1.062068965517248</v>
+        <v>3.387499999999998</v>
       </c>
       <c r="E34" t="n">
-        <v>1.104563505909455</v>
+        <v>5.232967160865206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.719544683942849</v>
+        <v>0.05174644243207986</v>
       </c>
       <c r="C35" t="n">
-        <v>18.66</v>
+        <v>6.32</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4464285714285714</v>
+        <v>-2.35324540987845</v>
       </c>
       <c r="E35" t="n">
-        <v>1.909018037880052</v>
+        <v>1.435613792631949</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.263378128269095</v>
+        <v>1.910185251928206</v>
       </c>
       <c r="C36" t="n">
-        <v>18.34</v>
+        <v>6.32</v>
       </c>
       <c r="D36" t="n">
-        <v>1.067644661776684</v>
+        <v>2.475597680011317</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8193203072284985</v>
+        <v>1.293479623263143</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.480077455872496</v>
+        <v>-0.9852216748768445</v>
       </c>
       <c r="C37" t="n">
-        <v>18.3</v>
+        <v>6.27</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4887734840384909</v>
+        <v>4.761904761904753</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1259064246332577</v>
+        <v>0.7322513380474275</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.900010614584437</v>
+        <v>2.235929067077877</v>
       </c>
       <c r="C38" t="n">
-        <v>18.22</v>
+        <v>6.25</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8177083333333357</v>
+        <v>5.788084464555062</v>
       </c>
       <c r="E38" t="n">
-        <v>3.266740182727033</v>
+        <v>13.40527698558425</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.63062743707905</v>
+        <v>-0.6988352745424293</v>
       </c>
       <c r="C39" t="n">
-        <v>18.18</v>
+        <v>6.22</v>
       </c>
       <c r="D39" t="n">
-        <v>1.972972972972973</v>
+        <v>3.558981233243962</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4830153754877891</v>
+        <v>1.090272623093852</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.359282495360965</v>
+        <v>0.04224578598284581</v>
       </c>
       <c r="C40" t="n">
-        <v>18.08</v>
+        <v>6.19</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.190045248868782</v>
+        <v>1.93403994763734</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1840943156571962</v>
+        <v>4.049593214048521</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.781226719642411</v>
+        <v>0.1386001386001356</v>
       </c>
       <c r="C41" t="n">
-        <v>17.79</v>
+        <v>6.18</v>
       </c>
       <c r="D41" t="n">
-        <v>0.04832085044697886</v>
+        <v>1.79930795847752</v>
       </c>
       <c r="E41" t="n">
-        <v>12.02334594834259</v>
+        <v>199.2925330605149</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8379491549495778</v>
+        <v>-0.5675702123495405</v>
       </c>
       <c r="C42" t="n">
-        <v>17.78</v>
+        <v>6.17</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4647887323943597</v>
+        <v>3.296919594528086</v>
       </c>
       <c r="E42" t="n">
-        <v>13.23907375070679</v>
+        <v>0.4213848302535453</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.091933779499832</v>
+        <v>0.4949293997767877</v>
       </c>
       <c r="C43" t="n">
-        <v>17.73</v>
+        <v>6.1</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2439024390243863</v>
+        <v>1.772005214620263</v>
       </c>
       <c r="E43" t="n">
-        <v>4.499327503170115</v>
+        <v>0.813005837272597</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.088887615336122</v>
+        <v>-0.3906249999999967</v>
       </c>
       <c r="C44" t="n">
-        <v>17.51</v>
+        <v>5.96</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1020466012812492</v>
+        <v>1.450240473547903</v>
       </c>
       <c r="E44" t="n">
-        <v>1.037702541743493</v>
+        <v>3.166558011355497</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.8813129980473927</v>
+        <v>1.598477640342526</v>
       </c>
       <c r="C45" t="n">
-        <v>17.21</v>
+        <v>5.95</v>
       </c>
       <c r="D45" t="n">
-        <v>1.719731657970395</v>
+        <v>-1.179996253980138</v>
       </c>
       <c r="E45" t="n">
-        <v>1.143167397714546</v>
+        <v>2.006196608326496</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-2.130187558346763</v>
+        <v>0.1264222503160556</v>
       </c>
       <c r="C46" t="n">
-        <v>17.14</v>
+        <v>5.95</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5289628858827531</v>
+        <v>1.452020202020202</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2640722183851532</v>
+        <v>10.10245788894532</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-4.100485146540842</v>
+        <v>-0.3733731598037124</v>
       </c>
       <c r="C47" t="n">
-        <v>16.94</v>
+        <v>5.92</v>
       </c>
       <c r="D47" t="n">
-        <v>2.113652113652114</v>
+        <v>0.2034479066281162</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8115270918445729</v>
+        <v>0.9574583935617456</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.02422285022203912</v>
+        <v>0.1556958740593532</v>
       </c>
       <c r="C48" t="n">
-        <v>16.77</v>
+        <v>5.91</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1292198352447027</v>
+        <v>3.290439588910951</v>
       </c>
       <c r="E48" t="n">
-        <v>1.0457982413989</v>
+        <v>0.4015395684390098</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.938310969399049</v>
+        <v>-1.434893388762243</v>
       </c>
       <c r="C49" t="n">
-        <v>16.46</v>
+        <v>5.87</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6195013874249666</v>
+        <v>-6.591836734693884</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5492456334140047</v>
+        <v>1.847381610475186</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.234682510211655</v>
+        <v>-0.4851799576570219</v>
       </c>
       <c r="C50" t="n">
-        <v>15.95</v>
+        <v>5.74</v>
       </c>
       <c r="D50" t="n">
-        <v>1.068317285648793</v>
+        <v>2.029961882811808</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3753240760763863</v>
+        <v>0.1349905913453399</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5985829464940114</v>
+        <v>0.5453905700211159</v>
       </c>
       <c r="C51" t="n">
-        <v>15.78</v>
+        <v>5.66</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.135397692774745</v>
+        <v>-1.6010498687664</v>
       </c>
       <c r="E51" t="n">
-        <v>0.06818366951099172</v>
+        <v>1.619406489692802</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8443908323280952</v>
+        <v>-0.2925687536571094</v>
       </c>
       <c r="C52" t="n">
-        <v>15.69</v>
+        <v>5.57</v>
       </c>
       <c r="D52" t="n">
-        <v>-3.588516746411478</v>
+        <v>-0.422535211267605</v>
       </c>
       <c r="E52" t="n">
-        <v>48.80526407540243</v>
+        <v>16.87955823273561</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5488223187742917</v>
+        <v>1.265822784810133</v>
       </c>
       <c r="C53" t="n">
-        <v>15.55</v>
+        <v>5.47</v>
       </c>
       <c r="D53" t="n">
-        <v>0.5913122583579765</v>
+        <v>1.012569832402235</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1530811870438026</v>
+        <v>2.134680903361071</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.547151277013755</v>
+        <v>1.141190642236734</v>
       </c>
       <c r="C54" t="n">
-        <v>15.47</v>
+        <v>5.42</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4111245465538061</v>
+        <v>-0.5704256252742375</v>
       </c>
       <c r="E54" t="n">
-        <v>7.076469615852935</v>
+        <v>0.6439166048104595</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.593103448275856</v>
+        <v>0.247411344268308</v>
       </c>
       <c r="C55" t="n">
-        <v>15.45</v>
+        <v>5.36</v>
       </c>
       <c r="D55" t="n">
-        <v>2.003226673837065</v>
+        <v>-0.2285191956124314</v>
       </c>
       <c r="E55" t="n">
-        <v>3.269415576507161</v>
+        <v>0.430662447422224</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.02423948612289971</v>
+        <v>0.9184128399464961</v>
       </c>
       <c r="C56" t="n">
-        <v>15.41</v>
+        <v>5.35</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.339435083040363</v>
+        <v>-1.802438593391047</v>
       </c>
       <c r="E56" t="n">
-        <v>1.125680092103807</v>
+        <v>1.043432824159081</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.567705271408964</v>
+        <v>-1.180109990834098</v>
       </c>
       <c r="C57" t="n">
-        <v>15.37</v>
+        <v>5.32</v>
       </c>
       <c r="D57" t="n">
-        <v>2.103029133706365</v>
+        <v>1.669565217391302</v>
       </c>
       <c r="E57" t="n">
-        <v>9.172434343002836</v>
+        <v>5.106083395189541</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3548835056318399</v>
+        <v>0.1832844574780058</v>
       </c>
       <c r="C58" t="n">
-        <v>14.96</v>
+        <v>5.17</v>
       </c>
       <c r="D58" t="n">
-        <v>1.491389913899146</v>
+        <v>-0.2927186242224703</v>
       </c>
       <c r="E58" t="n">
-        <v>4.031488612661196</v>
+        <v>4.685022089177117</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6109357499236331</v>
+        <v>-1.440205743677664</v>
       </c>
       <c r="C59" t="n">
-        <v>14.84</v>
+        <v>5.14</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.02048970392378296</v>
+        <v>-0.2348438723145208</v>
       </c>
       <c r="E59" t="n">
-        <v>0.371618378413661</v>
+        <v>1.512494139938274</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5399151561897328</v>
+        <v>0.6997053872053848</v>
       </c>
       <c r="C60" t="n">
-        <v>14.84</v>
+        <v>5.09</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.3489724699495987</v>
+        <v>-0.2925656966720604</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9591518871701827</v>
+        <v>0.659162125118829</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.529214178378852</v>
+        <v>3.411110072009739</v>
       </c>
       <c r="C61" t="n">
-        <v>14.84</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>-3.447037701974873</v>
+        <v>-0.2848680789491615</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4330998986147017</v>
+        <v>0.5060260968082197</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.768020205945211</v>
+        <v>2.805702796563693</v>
       </c>
       <c r="C62" t="n">
-        <v>14.62</v>
+        <v>4.86</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.1186708860759494</v>
+        <v>1.431238332296204</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02545776616426859</v>
+        <v>15.26864313526325</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.03249390739237132</v>
+        <v>2.540603838908411</v>
       </c>
       <c r="C63" t="n">
-        <v>14.58</v>
+        <v>4.77</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.4060419035244437</v>
+        <v>1.082423038728896</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5548320403015184</v>
+        <v>5.064647875402065</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6336149399733265</v>
+        <v>-0.4996156802459646</v>
       </c>
       <c r="C64" t="n">
-        <v>14.48</v>
+        <v>4.75</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1118693366148339</v>
+        <v>1.4059482425647</v>
       </c>
       <c r="E64" t="n">
-        <v>1.200325780867127</v>
+        <v>6.387167360107305</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-4.365153264553625</v>
+        <v>0.7354198734393759</v>
       </c>
       <c r="C65" t="n">
-        <v>14.39</v>
+        <v>4.69</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.4907115317209919</v>
+        <v>2.77306168647425</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1723558032270826</v>
+        <v>0.3926640166165306</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9191080474176149</v>
+        <v>0.1940167730629701</v>
       </c>
       <c r="C66" t="n">
-        <v>14.27</v>
+        <v>4.64</v>
       </c>
       <c r="D66" t="n">
-        <v>2.082794307891333</v>
+        <v>0.1061902679742531</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2018997604271502</v>
+        <v>18.6294438801422</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9159854230276722</v>
+        <v>2.795655671761866</v>
       </c>
       <c r="C67" t="n">
-        <v>14.21</v>
+        <v>4.64</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9045725646123283</v>
+        <v>-1.983956172960275</v>
       </c>
       <c r="E67" t="n">
-        <v>1.045764278252628</v>
+        <v>0.3069549165917881</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.262076769083471</v>
+        <v>-1.743817374762207</v>
       </c>
       <c r="C68" t="n">
-        <v>14.2</v>
+        <v>4.57</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7933709449929478</v>
+        <v>-1.719448670077913</v>
       </c>
       <c r="E68" t="n">
-        <v>0.06126261710983708</v>
+        <v>0.1696548911981873</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5071950931823623</v>
+        <v>-0.1963350785340256</v>
       </c>
       <c r="C69" t="n">
-        <v>13.95</v>
+        <v>4.56</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9036498063607611</v>
+        <v>1.133489461358308</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4889008172647409</v>
+        <v>4.549423923376438</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.9705266384022067</v>
+        <v>1.466939920181213</v>
       </c>
       <c r="C70" t="n">
-        <v>13.71</v>
+        <v>4.45</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.047199878585524</v>
+        <v>8.302328053577114</v>
       </c>
       <c r="E70" t="n">
-        <v>0.3706491020595199</v>
+        <v>1.303097449570913</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.537352870526071</v>
+        <v>0.05240174672488288</v>
       </c>
       <c r="C71" t="n">
-        <v>13.67</v>
+        <v>4.24</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.3842400585508633</v>
+        <v>0.5412011173184398</v>
       </c>
       <c r="E71" t="n">
-        <v>2.787556274678007</v>
+        <v>4.877359895690901</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7793507793507793</v>
+        <v>1.326963906581741</v>
       </c>
       <c r="C72" t="n">
-        <v>13.63</v>
+        <v>4.23</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.2341255764455481</v>
+        <v>1.173389209009958</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2428853178645353</v>
+        <v>0.500464328502038</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7677067855373862</v>
+        <v>2.504358852433043</v>
       </c>
       <c r="C73" t="n">
-        <v>13.62</v>
+        <v>4.21</v>
       </c>
       <c r="D73" t="n">
-        <v>0.06144015728680265</v>
+        <v>-1.499922684397718</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7013379091597279</v>
+        <v>1.096391911161464</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7508569563088406</v>
+        <v>-0.4980286366466025</v>
       </c>
       <c r="C74" t="n">
-        <v>13.58</v>
+        <v>4.2</v>
       </c>
       <c r="D74" t="n">
-        <v>1.332163806808847</v>
+        <v>-1.923879040667366</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8879500083713849</v>
+        <v>3.464981654751208</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.03603603603603604</v>
+        <v>0.748306751147042</v>
       </c>
       <c r="C75" t="n">
-        <v>13.57</v>
+        <v>4.16</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9221902017291034</v>
+        <v>2.48305773922472</v>
       </c>
       <c r="E75" t="n">
-        <v>3.515558437705885</v>
+        <v>1.023818302275006</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.506357103372034</v>
+        <v>0.7726770988896885</v>
       </c>
       <c r="C76" t="n">
-        <v>13.53</v>
+        <v>4.08</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.501332959169347</v>
+        <v>1.353092783505155</v>
       </c>
       <c r="E76" t="n">
-        <v>3.592833882271529</v>
+        <v>0.3535863577763019</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.6211180124223618</v>
+        <v>-0.3033072959946893</v>
       </c>
       <c r="C77" t="n">
-        <v>13.49</v>
+        <v>4.05</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.4757462686567211</v>
+        <v>-0.4730152115023926</v>
       </c>
       <c r="E77" t="n">
-        <v>3.601699590133812</v>
+        <v>0.4564686942480238</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.783375314861453</v>
+        <v>0.2517482517482518</v>
       </c>
       <c r="C78" t="n">
-        <v>13.46</v>
+        <v>3.98</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.3430952089204768</v>
+        <v>0.1562499999999975</v>
       </c>
       <c r="E78" t="n">
-        <v>22.7554780830245</v>
+        <v>0.3622865146957326</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.2810622213607377</v>
+        <v>-0.04788125448886488</v>
       </c>
       <c r="C79" t="n">
-        <v>13.45</v>
+        <v>3.93</v>
       </c>
       <c r="D79" t="n">
-        <v>0.720015463419353</v>
+        <v>1.365269461077842</v>
       </c>
       <c r="E79" t="n">
-        <v>3.016679884875548</v>
+        <v>0.7717595486450235</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4238068914685746</v>
+        <v>0.2429543245869777</v>
       </c>
       <c r="C80" t="n">
-        <v>13.17</v>
+        <v>3.74</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.412844036697256</v>
+        <v>1.320891904992726</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1860381751070834</v>
+        <v>5.946273407691005</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.970266881604872</v>
+        <v>0.7549834338167449</v>
       </c>
       <c r="C81" t="n">
-        <v>13.01</v>
+        <v>3.72</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.4567878677142335</v>
+        <v>0.9757412398921784</v>
       </c>
       <c r="E81" t="n">
-        <v>3.476679391348578</v>
+        <v>2.943718176609238</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.222465421692358</v>
+        <v>0.06356268870173074</v>
       </c>
       <c r="C82" t="n">
-        <v>12.98</v>
+        <v>3.66</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7729290791562065</v>
+        <v>0.754327457519456</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1916293580620416</v>
+        <v>18.27177257100442</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2.275960170697015</v>
+        <v>0.7925165648954019</v>
       </c>
       <c r="C83" t="n">
-        <v>12.71</v>
+        <v>3.6</v>
       </c>
       <c r="D83" t="n">
-        <v>0.5563282336578587</v>
+        <v>5.078628512503235</v>
       </c>
       <c r="E83" t="n">
-        <v>275.8021967787548</v>
+        <v>0.262606864736753</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.2027357677160725</v>
+        <v>-0.5549149610838727</v>
       </c>
       <c r="C84" t="n">
-        <v>12.68</v>
+        <v>3.58</v>
       </c>
       <c r="D84" t="n">
-        <v>2.418604651162791</v>
+        <v>0.5072831364591637</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1509998829863476</v>
+        <v>7.487065948483546</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-1.333823935240548</v>
+        <v>1.14219712525667</v>
       </c>
       <c r="C85" t="n">
-        <v>12.53</v>
+        <v>3.55</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.258623904531046</v>
+        <v>0.0634437254155564</v>
       </c>
       <c r="E85" t="n">
-        <v>0.3777110484502855</v>
+        <v>2.122658010053261</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-1.755359744674943</v>
+        <v>1.146941489361698</v>
       </c>
       <c r="C86" t="n">
-        <v>12.45</v>
+        <v>3.51</v>
       </c>
       <c r="D86" t="n">
-        <v>0.8403954802259951</v>
+        <v>0.2300739523418204</v>
       </c>
       <c r="E86" t="n">
-        <v>1.109679735490771</v>
+        <v>1.733405851597192</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.1360081604896345</v>
+        <v>2.247064137308037</v>
       </c>
       <c r="C87" t="n">
-        <v>12.2</v>
+        <v>3.48</v>
       </c>
       <c r="D87" t="n">
-        <v>0.7526881720430082</v>
+        <v>-1.76697956929873</v>
       </c>
       <c r="E87" t="n">
-        <v>0.4153650335080932</v>
+        <v>0.3935059935409098</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.7064364207221351</v>
+        <v>-0.9678426475179519</v>
       </c>
       <c r="C88" t="n">
-        <v>12.12</v>
+        <v>3.48</v>
       </c>
       <c r="D88" t="n">
-        <v>2.498023715415012</v>
+        <v>1.897856242118531</v>
       </c>
       <c r="E88" t="n">
-        <v>1.804253406463771</v>
+        <v>0.2549570424919587</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.08614088820825647</v>
+        <v>0.6037374221370481</v>
       </c>
       <c r="C89" t="n">
-        <v>11.9</v>
+        <v>3.45</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.5268703898840885</v>
+        <v>0.1428843589255015</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2644237900164801</v>
+        <v>7.586272724017137</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-1.343101343101343</v>
+        <v>-0.2515417072379209</v>
       </c>
       <c r="C90" t="n">
-        <v>11.88</v>
+        <v>3.44</v>
       </c>
       <c r="D90" t="n">
-        <v>2.413366336633664</v>
+        <v>-1.171398356788405</v>
       </c>
       <c r="E90" t="n">
-        <v>0.01107888444862026</v>
+        <v>0.5056663541300412</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.768431983385252</v>
+        <v>0.4372981700753498</v>
       </c>
       <c r="C91" t="n">
-        <v>11.81</v>
+        <v>3.41</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1883633319380446</v>
+        <v>2.592270078370944</v>
       </c>
       <c r="E91" t="n">
-        <v>1.951986989992281</v>
+        <v>0.8853507409722493</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-2.622002426052069</v>
+        <v>-0.5137808508594939</v>
       </c>
       <c r="C92" t="n">
-        <v>11.54</v>
+        <v>3.38</v>
       </c>
       <c r="D92" t="n">
-        <v>0.5461862782675425</v>
+        <v>-0.6564023360200738</v>
       </c>
       <c r="E92" t="n">
-        <v>5.344317050215839</v>
+        <v>0.6263323501451993</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-3.824917980315272</v>
+        <v>-0.2381094112744806</v>
       </c>
       <c r="C93" t="n">
-        <v>11.52</v>
+        <v>3.36</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.289624760795407</v>
+        <v>2.183901187421678</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9138628276282765</v>
+        <v>1.591677410113164</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.817290228841264</v>
+        <v>0.3064351378958121</v>
       </c>
       <c r="C94" t="n">
-        <v>11.5</v>
+        <v>3.36</v>
       </c>
       <c r="D94" t="n">
-        <v>0.6225965940303932</v>
+        <v>0.7942973523421543</v>
       </c>
       <c r="E94" t="n">
-        <v>1.217623105128409</v>
+        <v>0.6982108905991588</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-1.775768298276647</v>
+        <v>0.1103240041806978</v>
       </c>
       <c r="C95" t="n">
-        <v>11.46</v>
+        <v>3.3</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.4536357571714446</v>
+        <v>1.577634707963575</v>
       </c>
       <c r="E95" t="n">
-        <v>1.41556536300368</v>
+        <v>4.126189104191898</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.1651632575276273</v>
+        <v>-0.208409954640171</v>
       </c>
       <c r="C96" t="n">
-        <v>11.37</v>
+        <v>3.29</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.6341958396752918</v>
+        <v>-3.230958230958243</v>
       </c>
       <c r="E96" t="n">
-        <v>1.230733940937558</v>
+        <v>8.521357076350093</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2.717448326513482</v>
+        <v>-2.086931491076569</v>
       </c>
       <c r="C97" t="n">
-        <v>11.34</v>
+        <v>3.27</v>
       </c>
       <c r="D97" t="n">
-        <v>1.746680286006129</v>
+        <v>-1.087755402028514</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3348328416195008</v>
+        <v>4.958852192965321</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-3.642762868455793</v>
+        <v>-0.02352249338430408</v>
       </c>
       <c r="C98" t="n">
-        <v>11.29</v>
+        <v>3.27</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.6666057894256191</v>
+        <v>1.052879242397511</v>
       </c>
       <c r="E98" t="n">
-        <v>0.4623453515994917</v>
+        <v>0.08546615163235274</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.08259587020649505</v>
+        <v>1.058408467267738</v>
       </c>
       <c r="C99" t="n">
-        <v>11.11</v>
+        <v>3.18</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.5305352511200189</v>
+        <v>2.317688130333592</v>
       </c>
       <c r="E99" t="n">
-        <v>0.792046043412861</v>
+        <v>0.1329131180737326</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2989153642497224</v>
+        <v>-5.855096882898068</v>
       </c>
       <c r="C100" t="n">
-        <v>11.06</v>
+        <v>3.17</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.344868939523732</v>
+        <v>-17.90454884414615</v>
       </c>
       <c r="E100" t="n">
-        <v>1.275772787612792</v>
+        <v>2.224442398848824</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2.414398595258999</v>
+        <v>-0.8725157537566706</v>
       </c>
       <c r="C101" t="n">
-        <v>10.98</v>
+        <v>3.1</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.3857693956279469</v>
+        <v>1.149144254278726</v>
       </c>
       <c r="E101" t="n">
-        <v>0.3825550421872691</v>
+        <v>1.147662160930317</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.5928344359481036</v>
+        <v>-0.4431080867225846</v>
       </c>
       <c r="C102" t="n">
-        <v>10.88</v>
+        <v>3.07</v>
       </c>
       <c r="D102" t="n">
-        <v>1.953327571305092</v>
+        <v>-1.515392359455299</v>
       </c>
       <c r="E102" t="n">
-        <v>4.128041326780923</v>
+        <v>13.70857058444349</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2.140234106036263</v>
+        <v>-0.5983978380465031</v>
       </c>
       <c r="C103" t="n">
-        <v>10.85</v>
+        <v>3.05</v>
       </c>
       <c r="D103" t="n">
-        <v>5.027807426549071</v>
+        <v>2.039032915817069</v>
       </c>
       <c r="E103" t="n">
-        <v>0.114325787765891</v>
+        <v>4.542216454402209</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.3437334743521976</v>
+        <v>1.914306626879117</v>
       </c>
       <c r="C104" t="n">
-        <v>10.67</v>
+        <v>2.98</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.274703557312247</v>
+        <v>2.734655543892603</v>
       </c>
       <c r="E104" t="n">
-        <v>1.157085654258886</v>
+        <v>0.9075355510411376</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-4.361637141111795</v>
+        <v>1.230488777486607</v>
       </c>
       <c r="C105" t="n">
-        <v>10.59</v>
+        <v>2.92</v>
       </c>
       <c r="D105" t="n">
-        <v>0.7792539601430791</v>
+        <v>1.34496342149691</v>
       </c>
       <c r="E105" t="n">
-        <v>2.737487963646697</v>
+        <v>0.5928518641507469</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-1.644780474864038</v>
+        <v>0.4310344827586101</v>
       </c>
       <c r="C106" t="n">
-        <v>10.58</v>
+        <v>2.82</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5664194200944094</v>
+        <v>1.108966788605006</v>
       </c>
       <c r="E106" t="n">
-        <v>2.045006740888524</v>
+        <v>0.4362409006263755</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-2.425994594934316</v>
+        <v>1.271956390066626</v>
       </c>
       <c r="C107" t="n">
-        <v>10.46</v>
+        <v>2.77</v>
       </c>
       <c r="D107" t="n">
-        <v>-1.165861513687595</v>
+        <v>0.1555023923444922</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9819125019137437</v>
+        <v>1.66792942857887</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5415587473510808</v>
+        <v>-1.101494885916609</v>
       </c>
       <c r="C108" t="n">
-        <v>10.39</v>
+        <v>2.72</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.2810304449648818</v>
+        <v>-0.8637345152858306</v>
       </c>
       <c r="E108" t="n">
-        <v>11.44380598446558</v>
+        <v>1.775672767642041</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.3586925079548768</v>
+        <v>1.406649616368279</v>
       </c>
       <c r="C109" t="n">
-        <v>10.3</v>
+        <v>2.72</v>
       </c>
       <c r="D109" t="n">
-        <v>0.7315798641351794</v>
+        <v>-0.1639344262295025</v>
       </c>
       <c r="E109" t="n">
-        <v>1.573912960416218</v>
+        <v>12.28701931215898</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-1.561395617811473</v>
+        <v>-1.817549352117583</v>
       </c>
       <c r="C110" t="n">
-        <v>10.15</v>
+        <v>2.69</v>
       </c>
       <c r="D110" t="n">
-        <v>2.127937336814615</v>
+        <v>0.8148804251550086</v>
       </c>
       <c r="E110" t="n">
-        <v>0.09403068517198221</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.05151393738194918</v>
+        <v>0.4633529907329337</v>
       </c>
       <c r="C111" t="n">
-        <v>9.970000000000001</v>
+        <v>2.65</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.355835240274602</v>
+        <v>0.2935010482180325</v>
       </c>
       <c r="E111" t="n">
-        <v>4.256944203061406</v>
+        <v>4.188055891966506</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.5316518298714145</v>
+        <v>0.2796136248093529</v>
       </c>
       <c r="C112" t="n">
-        <v>9.880000000000001</v>
+        <v>2.54</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.8079552517091362</v>
+        <v>3.422053231939149</v>
       </c>
       <c r="E112" t="n">
-        <v>0.04646980954900391</v>
+        <v>8.809582991496399</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.3448275862068966</v>
+        <v>1.041217423448961</v>
       </c>
       <c r="C113" t="n">
-        <v>9.869999999999999</v>
+        <v>2.53</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.391752577319592</v>
+        <v>3.274390243902442</v>
       </c>
       <c r="E113" t="n">
-        <v>2.682563718709793</v>
+        <v>0.7670478962378404</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.1398450946643669</v>
+        <v>-0.6360796416876846</v>
       </c>
       <c r="C114" t="n">
-        <v>9.81</v>
+        <v>2.52</v>
       </c>
       <c r="D114" t="n">
-        <v>1.417982597486309</v>
+        <v>3.234848484848488</v>
       </c>
       <c r="E114" t="n">
-        <v>1.302818065528176</v>
+        <v>0.741248567540467</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.09418560843903052</v>
+        <v>0.04027386226339106</v>
       </c>
       <c r="C115" t="n">
-        <v>9.640000000000001</v>
+        <v>2.51</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1129163791481201</v>
+        <v>0.273752012882455</v>
       </c>
       <c r="E115" t="n">
-        <v>12.39017419644655</v>
+        <v>0.8089851838106028</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1.961140366805875</v>
+        <v>1.292790393647403</v>
       </c>
       <c r="C116" t="n">
-        <v>9.57</v>
+        <v>2.32</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.9260908281389217</v>
+        <v>-0.04780114722753346</v>
       </c>
       <c r="E116" t="n">
-        <v>0.5245424859059576</v>
+        <v>2.123780781602011</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-1.223739715156834</v>
+        <v>-1.189730745147151</v>
       </c>
       <c r="C117" t="n">
-        <v>9.34</v>
+        <v>2.28</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.02536997885835192</v>
+        <v>2.636248415716091</v>
       </c>
       <c r="E117" t="n">
-        <v>2.44880201634954</v>
+        <v>0.1457792091521142</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-1.278454931360623</v>
+        <v>-0.7402122536341706</v>
       </c>
       <c r="C118" t="n">
-        <v>9.33</v>
+        <v>1.97</v>
       </c>
       <c r="D118" t="n">
-        <v>-3.698953932810309</v>
+        <v>0.1437556154537205</v>
       </c>
       <c r="E118" t="n">
-        <v>0.09686846524522055</v>
+        <v>0.6912081168366084</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-2.339877057307159</v>
+        <v>3.492799205429568</v>
       </c>
       <c r="C119" t="n">
-        <v>9.289999999999999</v>
+        <v>1.86</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3857868020304568</v>
+        <v>-0.8797184900831734</v>
       </c>
       <c r="E119" t="n">
-        <v>1.0170163322933</v>
+        <v>4.100850441457983</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.1815904821540445</v>
+        <v>2.016283263209666</v>
       </c>
       <c r="C120" t="n">
-        <v>9.26</v>
+        <v>1.81</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.4500281267579253</v>
+        <v>4.916979110873056</v>
       </c>
       <c r="E120" t="n">
-        <v>0.407586146326501</v>
+        <v>0.3438000546939095</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.4051548515576675</v>
+        <v>1.307779030439687</v>
       </c>
       <c r="C121" t="n">
-        <v>9.220000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="D121" t="n">
-        <v>0.7009882785566537</v>
+        <v>0.9180948141553527</v>
       </c>
       <c r="E121" t="n">
-        <v>0.2390915282911682</v>
+        <v>0.5554402534151137</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-2.404058226731358</v>
+        <v>-1.054992523675033</v>
       </c>
       <c r="C122" t="n">
-        <v>9.17</v>
+        <v>1.74</v>
       </c>
       <c r="D122" t="n">
-        <v>-1.610169491525424</v>
+        <v>0.2686592225673786</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1607876372024875</v>
+        <v>0.6573772479847899</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-1.228733459357275</v>
+        <v>-0.1867914805908779</v>
       </c>
       <c r="C123" t="n">
-        <v>9.140000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.09569377990430078</v>
+        <v>0.2581255780937426</v>
       </c>
       <c r="E123" t="n">
-        <v>0.3633618844876248</v>
+        <v>0.1896857216340457</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-2.898047119327256</v>
+        <v>-0.7381173043823557</v>
       </c>
       <c r="C124" t="n">
-        <v>9.119999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.2433438305181816</v>
+        <v>-2.15412317849878</v>
       </c>
       <c r="E124" t="n">
-        <v>3.964776502597252</v>
+        <v>0.2744030876014116</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.07940709370037356</v>
+        <v>1.852988567482551</v>
       </c>
       <c r="C125" t="n">
-        <v>9.01</v>
+        <v>1.6</v>
       </c>
       <c r="D125" t="n">
-        <v>2.274530547474204</v>
+        <v>3.755320351048997</v>
       </c>
       <c r="E125" t="n">
-        <v>1.57142993601927</v>
+        <v>0.3066672038389915</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-1.361720523073588</v>
+        <v>-2.521873391662378</v>
       </c>
       <c r="C126" t="n">
-        <v>8.92</v>
+        <v>1.57</v>
       </c>
       <c r="D126" t="n">
-        <v>2.257039552974681</v>
+        <v>3.998592045054555</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1673427897699819</v>
+        <v>1.418633042934719</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-1.185770750988148</v>
+        <v>2.616033755274262</v>
       </c>
       <c r="C127" t="n">
-        <v>8.81</v>
+        <v>1.55</v>
       </c>
       <c r="D127" t="n">
-        <v>0.03529411764705347</v>
+        <v>3.769736842105261</v>
       </c>
       <c r="E127" t="n">
-        <v>0.1458759586297038</v>
+        <v>0.8543038083890039</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.8709921736935088</v>
+        <v>0.3209969788519638</v>
       </c>
       <c r="C128" t="n">
-        <v>8.779999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="D128" t="n">
-        <v>1.222462753087984</v>
+        <v>1.402220967438359</v>
       </c>
       <c r="E128" t="n">
-        <v>15.41823598071636</v>
+        <v>0.0374873031995937</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-3.473139027114862</v>
+        <v>0.4021937842778877</v>
       </c>
       <c r="C129" t="n">
-        <v>8.67</v>
+        <v>1.2</v>
       </c>
       <c r="D129" t="n">
-        <v>0.231457127827464</v>
+        <v>-2.257829570284066</v>
       </c>
       <c r="E129" t="n">
-        <v>0.1929318977889727</v>
+        <v>1.290540232579339</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-2.889426957223564</v>
+        <v>0.2243409983174434</v>
       </c>
       <c r="C130" t="n">
-        <v>8.640000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9142287234042553</v>
+        <v>-0.3437524982013005</v>
       </c>
       <c r="E130" t="n">
-        <v>3.155857674251504</v>
+        <v>1.814661304710187</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.5915637860082334</v>
+        <v>-0.4688672168042011</v>
       </c>
       <c r="C131" t="n">
-        <v>8.58</v>
+        <v>1.15</v>
       </c>
       <c r="D131" t="n">
-        <v>2.115135834411387</v>
+        <v>-0.7411594749073522</v>
       </c>
       <c r="E131" t="n">
-        <v>1.229978526270096</v>
+        <v>0.4397976325350627</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-2.231208029460618</v>
+        <v>2.205382298649572</v>
       </c>
       <c r="C132" t="n">
-        <v>8.44</v>
+        <v>1.14</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.2658788774002887</v>
+        <v>0.4087452471482847</v>
       </c>
       <c r="E132" t="n">
-        <v>0.4939451404973107</v>
+        <v>0.4466445449336511</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.8438081936685289</v>
+        <v>1.84662870523123</v>
       </c>
       <c r="C133" t="n">
-        <v>8.289999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2019735703156559</v>
+        <v>4.018183718256876</v>
       </c>
       <c r="E133" t="n">
-        <v>0.09647443968105422</v>
+        <v>1.460141813493769</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-1.786302814580455</v>
+        <v>2.245407121796314</v>
       </c>
       <c r="C134" t="n">
-        <v>8.210000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.5973154362416017</v>
+        <v>0.3216503992901578</v>
       </c>
       <c r="E134" t="n">
-        <v>19.79418890567293</v>
+        <v>3.718427696605071</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-0.5055611729019212</v>
+        <v>1.719951436665317</v>
       </c>
       <c r="C135" t="n">
-        <v>8.15</v>
+        <v>0.74</v>
       </c>
       <c r="D135" t="n">
-        <v>1.487804878048777</v>
+        <v>-0.603408262051588</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3510170768291476</v>
+        <v>0.08858500670651509</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-0.324402258800905</v>
+        <v>0.9329552730266208</v>
       </c>
       <c r="C136" t="n">
-        <v>8.06</v>
+        <v>0.71</v>
       </c>
       <c r="D136" t="n">
-        <v>0.8437801350048216</v>
+        <v>-1.699139102854553</v>
       </c>
       <c r="E136" t="n">
-        <v>0.8709124491116648</v>
+        <v>0.3379648168405152</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-1.198695091419464</v>
+        <v>0.02343933119774627</v>
       </c>
       <c r="C137" t="n">
-        <v>8.01</v>
+        <v>0.7</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.6450126698917196</v>
+        <v>0.9685986564599175</v>
       </c>
       <c r="E137" t="n">
-        <v>3.650416274078345</v>
+        <v>0.1990776913961272</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-0.6169887124545671</v>
+        <v>0.6816020289548818</v>
       </c>
       <c r="C138" t="n">
-        <v>7.52</v>
+        <v>0.68</v>
       </c>
       <c r="D138" t="n">
-        <v>-1.159824823138742</v>
+        <v>0.7137234321700293</v>
       </c>
       <c r="E138" t="n">
-        <v>4.462504288510559</v>
+        <v>0.1834944036410517</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.263468701735247</v>
+        <v>0.1060195547178675</v>
       </c>
       <c r="C139" t="n">
-        <v>7.52</v>
+        <v>0.61</v>
       </c>
       <c r="D139" t="n">
-        <v>-2.881478796665454</v>
+        <v>1.823958578489056</v>
       </c>
       <c r="E139" t="n">
-        <v>1.376171828047774</v>
+        <v>2.887700462944876</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-0.7628062360801807</v>
+        <v>3.190772226799501</v>
       </c>
       <c r="C140" t="n">
-        <v>7.43</v>
+        <v>0.6</v>
       </c>
       <c r="D140" t="n">
-        <v>1.565393031476188</v>
+        <v>-0.6024533643028203</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4493478147236076</v>
+        <v>0.7647567748824732</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-1.150270372829902</v>
+        <v>0.1629561624971394</v>
       </c>
       <c r="C141" t="n">
-        <v>7.27</v>
+        <v>0.59</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.5878260035029632</v>
+        <v>-1.031140441328109</v>
       </c>
       <c r="E141" t="n">
-        <v>0.7182425345422444</v>
+        <v>0.1544187307106301</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-0.1382488479262673</v>
+        <v>1.403230076780522</v>
       </c>
       <c r="C142" t="n">
-        <v>6.96</v>
+        <v>0.44</v>
       </c>
       <c r="D142" t="n">
-        <v>2.814951545916013</v>
+        <v>5.465622280243687</v>
       </c>
       <c r="E142" t="n">
-        <v>0.05132521278043808</v>
+        <v>1.008430756859528</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-2.238314680710994</v>
+        <v>2.954029015906306</v>
       </c>
       <c r="C143" t="n">
-        <v>6.83</v>
+        <v>0.36</v>
       </c>
       <c r="D143" t="n">
-        <v>2.222222222222222</v>
+        <v>-0.4414261460101834</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4493096061840521</v>
+        <v>49.23852282494042</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-0.6680220737728758</v>
+        <v>0.6328631338162409</v>
       </c>
       <c r="C144" t="n">
-        <v>6.71</v>
+        <v>0.31</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.630116959064324</v>
+        <v>-0.6591907864828005</v>
       </c>
       <c r="E144" t="n">
-        <v>3.34378053863958</v>
+        <v>0.2351992746545819</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.3618561089825433</v>
+        <v>1.34591050270333</v>
       </c>
       <c r="C145" t="n">
-        <v>6.68</v>
+        <v>0.31</v>
       </c>
       <c r="D145" t="n">
-        <v>0.7953340402969247</v>
+        <v>-0.6413166855845605</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3988618631279898</v>
+        <v>0.4978281146228073</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-1.361002560301849</v>
+        <v>-1.973775979913513</v>
       </c>
       <c r="C146" t="n">
-        <v>6.55</v>
+        <v>0.17</v>
       </c>
       <c r="D146" t="n">
-        <v>0.8333333333333365</v>
+        <v>-3.678406261117043</v>
       </c>
       <c r="E146" t="n">
-        <v>3.183515615485178</v>
+        <v>0.9854410022007787</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1.627716649995441</v>
+        <v>-1.068546921567205</v>
       </c>
       <c r="C147" t="n">
-        <v>6.47</v>
+        <v>0.17</v>
       </c>
       <c r="D147" t="n">
-        <v>0.9305654974946396</v>
+        <v>-2.358559882439376</v>
       </c>
       <c r="E147" t="n">
-        <v>1.43517403857099</v>
+        <v>0.9955748394994205</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-1.823500124471002</v>
+        <v>-0.5699346405228806</v>
       </c>
       <c r="C148" t="n">
-        <v>6.38</v>
+        <v>-0.05</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.03169572107766172</v>
+        <v>3.055321834244854</v>
       </c>
       <c r="E148" t="n">
-        <v>16.55230735798297</v>
+        <v>1.342686642965973</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4121967975479551</v>
+        <v>-1.368225292242297</v>
       </c>
       <c r="C149" t="n">
-        <v>6.35</v>
+        <v>-0.1</v>
       </c>
       <c r="D149" t="n">
-        <v>0.1263091416241298</v>
+        <v>-0.2693602693602732</v>
       </c>
       <c r="E149" t="n">
-        <v>0.2922735699591726</v>
+        <v>10.42461315453634</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-3.265231108524517</v>
+        <v>0.4948073449729113</v>
       </c>
       <c r="C150" t="n">
-        <v>6.35</v>
+        <v>-0.23</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.146258826509605</v>
+        <v>1.544509969109801</v>
       </c>
       <c r="E150" t="n">
-        <v>0.2959299149249719</v>
+        <v>0.4333556341237905</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.1886970468912161</v>
+        <v>0.8253842732170156</v>
       </c>
       <c r="C151" t="n">
-        <v>6.26</v>
+        <v>-0.25</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.1506733214050287</v>
+        <v>0.9901960784313775</v>
       </c>
       <c r="E151" t="n">
-        <v>0.01388668143179073</v>
+        <v>4.517619659204855</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.1252522441027195</v>
+        <v>-0.8017057569296453</v>
       </c>
       <c r="C152" t="n">
-        <v>5.9</v>
+        <v>-0.29</v>
       </c>
       <c r="D152" t="n">
-        <v>-2.376815623045385</v>
+        <v>-1.564783767517825</v>
       </c>
       <c r="E152" t="n">
-        <v>0.6545390816312181</v>
+        <v>1.774933341797867</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-1.154938118470743</v>
+        <v>0.4622852299869019</v>
       </c>
       <c r="C153" t="n">
-        <v>5.83</v>
+        <v>-0.45</v>
       </c>
       <c r="D153" t="n">
-        <v>0.3876185164528748</v>
+        <v>1.809954751131215</v>
       </c>
       <c r="E153" t="n">
-        <v>0.1068615903614714</v>
+        <v>0.4827172943443893</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-2.100439182738209</v>
+        <v>-3.882151867827783</v>
       </c>
       <c r="C154" t="n">
-        <v>5.66</v>
+        <v>-0.5</v>
       </c>
       <c r="D154" t="n">
-        <v>0.3803393797542422</v>
+        <v>-0.1467682754727581</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1252605941799373</v>
+        <v>0.3460069376619656</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1.722553973357832</v>
+        <v>0.9559177498108858</v>
       </c>
       <c r="C155" t="n">
-        <v>5.56</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.8692707157371791</v>
+        <v>-0.4359673024523222</v>
       </c>
       <c r="E155" t="n">
-        <v>5.678272952785124</v>
+        <v>1.146812858928781</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-2.30158439752644</v>
+        <v>-0.3914259086672922</v>
       </c>
       <c r="C156" t="n">
-        <v>5.56</v>
+        <v>-0.68</v>
       </c>
       <c r="D156" t="n">
-        <v>2.584269662921348</v>
+        <v>3.695733532934132</v>
       </c>
       <c r="E156" t="n">
-        <v>0.2622209615762721</v>
+        <v>0.5658288406193435</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-1.986176791560567</v>
+        <v>0.8036289951183485</v>
       </c>
       <c r="C157" t="n">
-        <v>5.53</v>
+        <v>-0.68</v>
       </c>
       <c r="D157" t="n">
-        <v>4.772862232779097</v>
+        <v>1.866276812024575</v>
       </c>
       <c r="E157" t="n">
-        <v>0.36048483452651</v>
+        <v>0.3269975485408446</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.6305972126543361</v>
+        <v>-3.886544065923029</v>
       </c>
       <c r="C158" t="n">
-        <v>5.41</v>
+        <v>-0.79</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.9689310163243829</v>
+        <v>-7.554173092505947</v>
       </c>
       <c r="E158" t="n">
-        <v>16.59660405684475</v>
+        <v>0.192874164941204</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-1.578924412265017</v>
+        <v>2.733916809528106</v>
       </c>
       <c r="C159" t="n">
-        <v>5.39</v>
+        <v>-1.1</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.8331486815865258</v>
+        <v>-0.8782715615668365</v>
       </c>
       <c r="E159" t="n">
-        <v>19.29416436199301</v>
+        <v>0.2631208409839695</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2.119829235978213</v>
+        <v>0.2281368821292776</v>
       </c>
       <c r="C160" t="n">
-        <v>4.88</v>
+        <v>-1.14</v>
       </c>
       <c r="D160" t="n">
-        <v>0.6775263082023929</v>
+        <v>3.59635811836116</v>
       </c>
       <c r="E160" t="n">
-        <v>0.1096261374005616</v>
+        <v>1.856479356304775</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-0.8643367155204782</v>
+        <v>0.512710959196748</v>
       </c>
       <c r="C161" t="n">
-        <v>4.83</v>
+        <v>-1.22</v>
       </c>
       <c r="D161" t="n">
-        <v>0.6886530199646255</v>
+        <v>0.03400637619554198</v>
       </c>
       <c r="E161" t="n">
-        <v>0.4246918972158445</v>
+        <v>9.821464266645831</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1.360872502654197</v>
+        <v>-1.219323969748414</v>
       </c>
       <c r="C162" t="n">
-        <v>4.81</v>
+        <v>-1.25</v>
       </c>
       <c r="D162" t="n">
-        <v>1.533041325461808</v>
+        <v>0.5312499999999964</v>
       </c>
       <c r="E162" t="n">
-        <v>0.9264448466364943</v>
+        <v>0.2982987101353023</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.475584432982779</v>
+        <v>0.7556174189699741</v>
       </c>
       <c r="C163" t="n">
-        <v>4.71</v>
+        <v>-1.25</v>
       </c>
       <c r="D163" t="n">
-        <v>-2.286666666666664</v>
+        <v>2.289323070850602</v>
       </c>
       <c r="E163" t="n">
-        <v>1.688068932450751</v>
+        <v>0.0125942493260929</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-1.865600609175701</v>
+        <v>1.179764047190565</v>
       </c>
       <c r="C164" t="n">
-        <v>4.56</v>
+        <v>-1.28</v>
       </c>
       <c r="D164" t="n">
-        <v>1.939864209505335</v>
+        <v>-1.133069828722006</v>
       </c>
       <c r="E164" t="n">
-        <v>0.2187372555283644</v>
+        <v>1.332597570027738</v>
       </c>
     </row>
     <row r="165">
@@ -3547,909 +3547,907 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.5351170568561949</v>
+        <v>3.661595050994813</v>
       </c>
       <c r="C165" t="n">
-        <v>4.35</v>
+        <v>-1.67</v>
       </c>
       <c r="D165" t="n">
-        <v>3.376580172987351</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="E165" t="n">
-        <v>7.181121744347193</v>
+        <v>4.399241935903947</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-1.818551254698771</v>
+        <v>0.06502601040415938</v>
       </c>
       <c r="C166" t="n">
-        <v>4.35</v>
+        <v>-1.74</v>
       </c>
       <c r="D166" t="n">
-        <v>0.5380794701986755</v>
+        <v>4.218945263684083</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1369075653173657</v>
+        <v>0.1950810479092602</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-1.656538749687838</v>
+        <v>0.3328961969131444</v>
       </c>
       <c r="C167" t="n">
-        <v>4.27</v>
+        <v>-1.74</v>
       </c>
       <c r="D167" t="n">
-        <v>0.8972405620450313</v>
+        <v>-0.9772772974059997</v>
       </c>
       <c r="E167" t="n">
-        <v>0.09813306176967627</v>
+        <v>0.3179942148168405</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-0.1074938574938645</v>
+        <v>1.027190332326284</v>
       </c>
       <c r="C168" t="n">
-        <v>4.09</v>
+        <v>-1.93</v>
       </c>
       <c r="D168" t="n">
-        <v>-1.79861644888548</v>
+        <v>-0.7296650717703377</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2080009212503426</v>
+        <v>7.545763826490083</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.3704823831846432</v>
+        <v>0.4643064422518838</v>
       </c>
       <c r="C169" t="n">
-        <v>3.97</v>
+        <v>-2.09</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.7269303201506659</v>
+        <v>0.9400766766451389</v>
       </c>
       <c r="E169" t="n">
-        <v>1.261037558198372</v>
+        <v>0.166015141748382</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-0.4428697962798938</v>
+        <v>0.1213994040392886</v>
       </c>
       <c r="C170" t="n">
-        <v>3.79</v>
+        <v>-2.51</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.07117437722419524</v>
+        <v>1.069223985890651</v>
       </c>
       <c r="E170" t="n">
-        <v>0.6267882724194576</v>
+        <v>8.692677608704145</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1.028115820394456</v>
+        <v>2.254080663269712</v>
       </c>
       <c r="C171" t="n">
-        <v>3.59</v>
+        <v>-2.51</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.6645898234683258</v>
+        <v>-0.7263513513513509</v>
       </c>
       <c r="E171" t="n">
-        <v>2.520570655151745</v>
+        <v>5.846099315023896</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>4.320337197049533</v>
+        <v>-0.6384272395622168</v>
       </c>
       <c r="C172" t="n">
-        <v>3.48</v>
+        <v>-2.59</v>
       </c>
       <c r="D172" t="n">
-        <v>-1.991341991341985</v>
+        <v>1.631820499745028</v>
       </c>
       <c r="E172" t="n">
-        <v>10.009770772643</v>
+        <v>0.5851080367490982</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-1.652606032589848</v>
+        <v>-0.7281761329563952</v>
       </c>
       <c r="C173" t="n">
-        <v>3.44</v>
+        <v>-2.69</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.2820211515863663</v>
+        <v>3.14981014842941</v>
       </c>
       <c r="E173" t="n">
-        <v>2.190997590473974</v>
+        <v>0.3479244800823013</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>-0.6915097963887865</v>
+        <v>0.4358112314780226</v>
       </c>
       <c r="C174" t="n">
-        <v>3.15</v>
+        <v>-2.74</v>
       </c>
       <c r="D174" t="n">
-        <v>-3.249516441005805</v>
+        <v>-1.330688486651801</v>
       </c>
       <c r="E174" t="n">
-        <v>4.138115379706648</v>
+        <v>0.5749078668073081</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.1387787470261703</v>
+        <v>0.2642555506619295</v>
       </c>
       <c r="C175" t="n">
-        <v>3.06</v>
+        <v>-2.84</v>
       </c>
       <c r="D175" t="n">
-        <v>1.059196198772528</v>
+        <v>2.291930441073881</v>
       </c>
       <c r="E175" t="n">
-        <v>3.606861723030011</v>
+        <v>1.025657303590265</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-4.134123350390525</v>
+        <v>1.00400031375011</v>
       </c>
       <c r="C176" t="n">
-        <v>2.57</v>
+        <v>-2.97</v>
       </c>
       <c r="D176" t="n">
-        <v>-5.66793088916983</v>
+        <v>-2.430690378193686</v>
       </c>
       <c r="E176" t="n">
-        <v>0.4937938983615701</v>
+        <v>2.505892617624461</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-2.095130237825588</v>
+        <v>-1.212440695835526</v>
       </c>
       <c r="C177" t="n">
-        <v>2.45</v>
+        <v>-2.97</v>
       </c>
       <c r="D177" t="n">
-        <v>1.850780798149212</v>
+        <v>-1.974386339381007</v>
       </c>
       <c r="E177" t="n">
-        <v>3.152767558614951</v>
+        <v>6.972716529280775</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1.415762151958471</v>
+        <v>-3.093569760236431</v>
       </c>
       <c r="C178" t="n">
-        <v>2.42</v>
+        <v>-2.98</v>
       </c>
       <c r="D178" t="n">
-        <v>-1.340158213122391</v>
+        <v>-2.602065912444668</v>
       </c>
       <c r="E178" t="n">
-        <v>0.2995658289355924</v>
+        <v>2.786952165618367</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2.436526562833365</v>
+        <v>2.660561811656973</v>
       </c>
       <c r="C179" t="n">
-        <v>2.33</v>
+        <v>-3.07</v>
       </c>
       <c r="D179" t="n">
-        <v>0.7664750479046943</v>
+        <v>4.737222757955641</v>
       </c>
       <c r="E179" t="n">
-        <v>0.5423980793840784</v>
+        <v>0.0178719674180568</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.1600000000000023</v>
+        <v>-0.9477224090492203</v>
       </c>
       <c r="C180" t="n">
-        <v>2.18</v>
+        <v>-3.19</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.05591054313099632</v>
+        <v>-0.9074074074074102</v>
       </c>
       <c r="E180" t="n">
-        <v>3.432482193891887</v>
+        <v>0.1301442389082054</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-2.062403657045658</v>
+        <v>-2.757619738751822</v>
       </c>
       <c r="C181" t="n">
-        <v>2.18</v>
+        <v>-3.23</v>
       </c>
       <c r="D181" t="n">
-        <v>-3.989145183175034</v>
+        <v>-4.878731343283578</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1654522630732243</v>
+        <v>1.544058304358584</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>4.223806911684042</v>
+        <v>-1.224399911913676</v>
       </c>
       <c r="C182" t="n">
-        <v>1.84</v>
+        <v>-3.24</v>
       </c>
       <c r="D182" t="n">
-        <v>-1.491228070175439</v>
+        <v>1.819235742631642</v>
       </c>
       <c r="E182" t="n">
-        <v>15.29603180436379</v>
+        <v>9.23683724329674</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>-2.950776863820342</v>
+        <v>-2.682748538011699</v>
       </c>
       <c r="C183" t="n">
-        <v>1.84</v>
+        <v>-3.34</v>
       </c>
       <c r="D183" t="n">
-        <v>1.304991255213238</v>
+        <v>1.652520093142042</v>
       </c>
       <c r="E183" t="n">
-        <v>0.08540802607520555</v>
+        <v>0.7024065320154705</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.3428571428571396</v>
+        <v>1.920581365169991</v>
       </c>
       <c r="C184" t="n">
-        <v>1.63</v>
+        <v>-3.53</v>
       </c>
       <c r="D184" t="n">
-        <v>-2.96697038724374</v>
+        <v>0.4583651642475201</v>
       </c>
       <c r="E184" t="n">
-        <v>6.496515991467821</v>
+        <v>1.934764083681682</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.9381472606912199</v>
+        <v>2.938417082598423</v>
       </c>
       <c r="C185" t="n">
-        <v>1.52</v>
+        <v>-3.69</v>
       </c>
       <c r="D185" t="n">
-        <v>2.426168825943499</v>
+        <v>0.03281079110463329</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1161980062041116</v>
+        <v>0.3146779896081572</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.0972373162500741</v>
+        <v>0.1559792027729636</v>
       </c>
       <c r="C186" t="n">
-        <v>1.18</v>
+        <v>-3.81</v>
       </c>
       <c r="D186" t="n">
-        <v>0.5485714285714234</v>
+        <v>0.04614408490511623</v>
       </c>
       <c r="E186" t="n">
-        <v>0.2876850958304666</v>
+        <v>0.1999058320636533</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>GODFRYPHLP</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-1.15413819286257</v>
+        <v>-0.8753932430584175</v>
       </c>
       <c r="C187" t="n">
-        <v>1.12</v>
+        <v>-3.89</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2842218466738397</v>
+        <v>-0.5795501586863488</v>
       </c>
       <c r="E187" t="n">
-        <v>0.390915548248762</v>
+        <v>0.1239264692476983</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1.647000983284166</v>
+        <v>1.86929430517316</v>
       </c>
       <c r="C188" t="n">
-        <v>0.77</v>
+        <v>-4.32</v>
       </c>
       <c r="D188" t="n">
-        <v>0.8343409915356684</v>
+        <v>-0.455192034139409</v>
       </c>
       <c r="E188" t="n">
-        <v>1.605137828019649</v>
+        <v>7.166058685262596</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-0.5370006548788504</v>
+        <v>-1.228906823184152</v>
       </c>
       <c r="C189" t="n">
-        <v>0.71</v>
+        <v>-4.63</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.2699499604951217</v>
+        <v>-3.073351903435469</v>
       </c>
       <c r="E189" t="n">
-        <v>0.115946731989118</v>
+        <v>0.2236407098488104</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.145509282488715</v>
+        <v>-0.9581279653599972</v>
       </c>
       <c r="C190" t="n">
-        <v>0.55</v>
+        <v>-4.67</v>
       </c>
       <c r="D190" t="n">
-        <v>0.1002054211132822</v>
+        <v>-1.813869122366402</v>
       </c>
       <c r="E190" t="n">
-        <v>0.1462832510478825</v>
+        <v>0.8702700348999232</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.09598244892363164</v>
+        <v>0.003308738378053437</v>
       </c>
       <c r="C191" t="n">
-        <v>0.43</v>
+        <v>-4.77</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.3287671232876681</v>
+        <v>3.040629962943359</v>
       </c>
       <c r="E191" t="n">
-        <v>2.818889134473098</v>
+        <v>0.1288607226107226</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-1.805027769657998</v>
+        <v>-2.923410075222245</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.37</v>
+        <v>-5.33</v>
       </c>
       <c r="D192" t="n">
-        <v>1.838207933318452</v>
+        <v>-1.379512767830933</v>
       </c>
       <c r="E192" t="n">
-        <v>0.4087997981315494</v>
+        <v>10.92469454428253</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-1.744966442953027</v>
+        <v>4.983706034385886</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.52</v>
+        <v>-5.44</v>
       </c>
       <c r="D193" t="n">
-        <v>0.379477838494232</v>
+        <v>0.09098207118009098</v>
       </c>
       <c r="E193" t="n">
-        <v>1.295600896945466</v>
+        <v>0.1245698551913636</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-2.067889908256877</v>
+        <v>1.953164945290929</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.77</v>
+        <v>-5.92</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5826916231053051</v>
+        <v>-2.843530591775326</v>
       </c>
       <c r="E194" t="n">
-        <v>0.7588730709662594</v>
+        <v>0.1841687176882708</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-0.002582577929286668</v>
+        <v>0.4511555105423017</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.85</v>
+        <v>-6.31</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.1652892561983495</v>
+        <v>0.241368774824323</v>
       </c>
       <c r="E195" t="n">
-        <v>1.083254284994843</v>
+        <v>0.6156059954942636</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1.178085325403188</v>
+        <v>-0.6538437123087637</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.87</v>
+        <v>-6.53</v>
       </c>
       <c r="D196" t="n">
-        <v>2.102645263395888</v>
+        <v>1.022364217252396</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1412590934334114</v>
+        <v>0.4145061758539412</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.7007832283139966</v>
+        <v>0.4173913043478287</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.99</v>
+        <v>-6.7</v>
       </c>
       <c r="D197" t="n">
-        <v>1.532163742690061</v>
+        <v>0.4156563907170099</v>
       </c>
       <c r="E197" t="n">
-        <v>4.855627971941135</v>
+        <v>1.650736251644073</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>-0.03341767317514767</v>
+        <v>0.8144188519772722</v>
       </c>
       <c r="C198" t="n">
-        <v>-1.73</v>
+        <v>-7.33</v>
       </c>
       <c r="D198" t="n">
-        <v>-2.979942693409746</v>
+        <v>-1.235356171228694</v>
       </c>
       <c r="E198" t="n">
-        <v>0.9054548262294194</v>
+        <v>0.12276218892839</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-0.7567983581323726</v>
+        <v>0.6438213914849429</v>
       </c>
       <c r="C199" t="n">
-        <v>-1.79</v>
+        <v>-8.06</v>
       </c>
       <c r="D199" t="n">
-        <v>0.1938735944164405</v>
+        <v>1.547668179942221</v>
       </c>
       <c r="E199" t="n">
-        <v>0.4725303154247609</v>
+        <v>0.1753782181505645</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-0.8610870654699531</v>
+        <v>6.052115438498185</v>
       </c>
       <c r="C200" t="n">
-        <v>-1.84</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.9604779411764707</v>
+        <v>-2.582562747688237</v>
       </c>
       <c r="E200" t="n">
-        <v>0.1243021966460862</v>
+        <v>1.174180161086586</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1.532864871587593</v>
+        <v>0.8979246082168572</v>
       </c>
       <c r="C201" t="n">
-        <v>-2</v>
+        <v>-8.56</v>
       </c>
       <c r="D201" t="n">
-        <v>0.5205940897259226</v>
+        <v>0.8983292754596592</v>
       </c>
       <c r="E201" t="n">
-        <v>0.7101831860668315</v>
+        <v>0.2234974638955086</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1.900610287707058</v>
+        <v>0.288328945718942</v>
       </c>
       <c r="C202" t="n">
-        <v>-2.27</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.2138945927446954</v>
+        <v>2.3375</v>
       </c>
       <c r="E202" t="n">
-        <v>1.327160354607088</v>
+        <v>0.01336297547889727</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>-1.46336014298481</v>
+        <v>-1.452020202020202</v>
       </c>
       <c r="C203" t="n">
-        <v>-2.33</v>
+        <v>-9.75</v>
       </c>
       <c r="D203" t="n">
-        <v>2.165287382382962</v>
+        <v>-1.65848103067834</v>
       </c>
       <c r="E203" t="n">
-        <v>2.053011429925406</v>
+        <v>0.1497555052024326</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-1.373877999633633</v>
+        <v>2.352655833131218</v>
       </c>
       <c r="C204" t="n">
-        <v>-2.94</v>
+        <v>-10.58</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.9286775631500743</v>
+        <v>-2.819905213270149</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2737872702413055</v>
+        <v>0.5291717128309307</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-2.215992524362576</v>
+        <v>-1.324198813738563</v>
       </c>
       <c r="C205" t="n">
-        <v>-3</v>
+        <v>-11.75</v>
       </c>
       <c r="D205" t="n">
-        <v>-1.105802047781578</v>
+        <v>1.122967242905736</v>
       </c>
       <c r="E205" t="n">
-        <v>0.0857885194482793</v>
+        <v>0.1075598051855035</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1.995984410062593</v>
+        <v>1.498620031468439</v>
       </c>
       <c r="C206" t="n">
-        <v>-3.25</v>
+        <v>-11.96</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.03473830477073508</v>
+        <v>0.731893265565443</v>
       </c>
       <c r="E206" t="n">
-        <v>1.135132194913435</v>
+        <v>0.2813118562071076</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.1412096963991581</v>
+        <v>-0.6147109595385372</v>
       </c>
       <c r="C207" t="n">
-        <v>-3.48</v>
+        <v>-12.62</v>
       </c>
       <c r="D207" t="n">
-        <v>0.8147277712495041</v>
+        <v>1.143825460707472</v>
       </c>
       <c r="E207" t="n">
-        <v>1.456904880106114</v>
+        <v>1.855473785990546</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.4550227511375534</v>
+        <v>4.342215988779804</v>
       </c>
       <c r="C208" t="n">
-        <v>-4.41</v>
+        <v>-13.05</v>
       </c>
       <c r="D208" t="n">
-        <v>2.613240418118467</v>
+        <v>-0.8280015054572827</v>
       </c>
       <c r="E208" t="n">
-        <v>18.2717415213526</v>
+        <v>0.06501209451628447</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-1.20954560313828</v>
+        <v>0.6397580551355124</v>
       </c>
       <c r="C209" t="n">
-        <v>-4.52</v>
+        <v>-15.82</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.143392896536505</v>
+        <v>-0.3536754507628336</v>
       </c>
       <c r="E209" t="n">
-        <v>5.176840530557413</v>
+        <v>0.6160129442252348</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-1.673066374108618</v>
+        <v>1.683831943763275</v>
       </c>
       <c r="C210" t="n">
-        <v>-5.74</v>
+        <v>-17</v>
       </c>
       <c r="D210" t="n">
-        <v>5.146443514644348</v>
+        <v>2.323151125401937</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3022688177720654</v>
+        <v>0.6186084632313683</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-1.067054183101513</v>
+        <v>0.1572551822730522</v>
       </c>
       <c r="C211" t="n">
-        <v>-6.28</v>
+        <v>-23.48</v>
       </c>
       <c r="D211" t="n">
-        <v>-1.028202115158632</v>
+        <v>-1.584356266057665</v>
       </c>
       <c r="E211" t="n">
-        <v>1.056012657640076</v>
+        <v>0.05731954265473819</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-2.397912022184765</v>
+        <v>3.793843951324274</v>
       </c>
       <c r="C212" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="D212" t="n">
-        <v>3.504178272980502</v>
-      </c>
+        <v>-25.38</v>
+      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>0.02742417926597681</v>
+        <v>27.35854584196065</v>
       </c>
     </row>
   </sheetData>

--- a/Output/FEATURES.xlsx
+++ b/Output/FEATURES.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E212"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>Volume Ratio</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -461,6 +466,9 @@
       <c r="E2" t="n">
         <v>1.007064223020927</v>
       </c>
+      <c r="F2" t="n">
+        <v>47.66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -480,6 +488,9 @@
       <c r="E3" t="n">
         <v>1.363086982849553</v>
       </c>
+      <c r="F3" t="n">
+        <v>44.16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -499,6 +510,9 @@
       <c r="E4" t="n">
         <v>1.314779319842169</v>
       </c>
+      <c r="F4" t="n">
+        <v>60.79</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,6 +532,9 @@
       <c r="E5" t="n">
         <v>0.5732511785235249</v>
       </c>
+      <c r="F5" t="n">
+        <v>55.07</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -537,6 +554,9 @@
       <c r="E6" t="n">
         <v>0.5022414736101887</v>
       </c>
+      <c r="F6" t="n">
+        <v>43.79</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -556,6 +576,9 @@
       <c r="E7" t="n">
         <v>2.924939934367309</v>
       </c>
+      <c r="F7" t="n">
+        <v>47.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -575,6 +598,9 @@
       <c r="E8" t="n">
         <v>1.564908322589887</v>
       </c>
+      <c r="F8" t="n">
+        <v>39.05</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -594,6 +620,9 @@
       <c r="E9" t="n">
         <v>7.73744441080335</v>
       </c>
+      <c r="F9" t="n">
+        <v>65.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -613,6 +642,9 @@
       <c r="E10" t="n">
         <v>0.6150684162206509</v>
       </c>
+      <c r="F10" t="n">
+        <v>46.85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -632,6 +664,9 @@
       <c r="E11" t="n">
         <v>1.514841827167246</v>
       </c>
+      <c r="F11" t="n">
+        <v>49.2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -651,6 +686,9 @@
       <c r="E12" t="n">
         <v>1.365947018530817</v>
       </c>
+      <c r="F12" t="n">
+        <v>71.15000000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -670,6 +708,9 @@
       <c r="E13" t="n">
         <v>2.21008361982524</v>
       </c>
+      <c r="F13" t="n">
+        <v>60.05</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -689,6 +730,9 @@
       <c r="E14" t="n">
         <v>2.460246399317628</v>
       </c>
+      <c r="F14" t="n">
+        <v>58.91</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -708,6 +752,9 @@
       <c r="E15" t="n">
         <v>6.337324686486697</v>
       </c>
+      <c r="F15" t="n">
+        <v>58.14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -727,6 +774,9 @@
       <c r="E16" t="n">
         <v>7.398603026396322</v>
       </c>
+      <c r="F16" t="n">
+        <v>41.82</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -746,6 +796,9 @@
       <c r="E17" t="n">
         <v>0.9621985323800967</v>
       </c>
+      <c r="F17" t="n">
+        <v>63.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -765,6 +818,9 @@
       <c r="E18" t="n">
         <v>0.1386523160266177</v>
       </c>
+      <c r="F18" t="n">
+        <v>52.46</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -784,6 +840,9 @@
       <c r="E19" t="n">
         <v>0.7430196084176531</v>
       </c>
+      <c r="F19" t="n">
+        <v>71.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -803,6 +862,9 @@
       <c r="E20" t="n">
         <v>0.417956694143845</v>
       </c>
+      <c r="F20" t="n">
+        <v>51.49</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -822,6 +884,9 @@
       <c r="E21" t="n">
         <v>4.208099337813025</v>
       </c>
+      <c r="F21" t="n">
+        <v>57.88</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -841,6 +906,9 @@
       <c r="E22" t="n">
         <v>1.579850259144952</v>
       </c>
+      <c r="F22" t="n">
+        <v>62.72</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -860,6 +928,9 @@
       <c r="E23" t="n">
         <v>1.64025406623172</v>
       </c>
+      <c r="F23" t="n">
+        <v>39.75</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -879,6 +950,9 @@
       <c r="E24" t="n">
         <v>6.038321548098084</v>
       </c>
+      <c r="F24" t="n">
+        <v>51.42</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -898,6 +972,9 @@
       <c r="E25" t="n">
         <v>0.4322357112161582</v>
       </c>
+      <c r="F25" t="n">
+        <v>50.96</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -917,6 +994,9 @@
       <c r="E26" t="n">
         <v>3.24571279511922</v>
       </c>
+      <c r="F26" t="n">
+        <v>36.18</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -936,6 +1016,9 @@
       <c r="E27" t="n">
         <v>2.806155669284161</v>
       </c>
+      <c r="F27" t="n">
+        <v>61.9</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -955,6 +1038,9 @@
       <c r="E28" t="n">
         <v>1.225934679845294</v>
       </c>
+      <c r="F28" t="n">
+        <v>53.95</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -974,6 +1060,9 @@
       <c r="E29" t="n">
         <v>0.3841506491646157</v>
       </c>
+      <c r="F29" t="n">
+        <v>59.88</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -993,6 +1082,9 @@
       <c r="E30" t="n">
         <v>0.6082308636428748</v>
       </c>
+      <c r="F30" t="n">
+        <v>66.42</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1012,6 +1104,9 @@
       <c r="E31" t="n">
         <v>9.818966008386399</v>
       </c>
+      <c r="F31" t="n">
+        <v>54.12</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1031,6 +1126,9 @@
       <c r="E32" t="n">
         <v>65.23126611516975</v>
       </c>
+      <c r="F32" t="n">
+        <v>39.53</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1050,6 +1148,9 @@
       <c r="E33" t="n">
         <v>1.833522971441966</v>
       </c>
+      <c r="F33" t="n">
+        <v>55.05</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1069,6 +1170,9 @@
       <c r="E34" t="n">
         <v>5.232967160865206</v>
       </c>
+      <c r="F34" t="n">
+        <v>47.43</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1088,6 +1192,9 @@
       <c r="E35" t="n">
         <v>1.435613792631949</v>
       </c>
+      <c r="F35" t="n">
+        <v>36.28</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1107,6 +1214,9 @@
       <c r="E36" t="n">
         <v>1.293479623263143</v>
       </c>
+      <c r="F36" t="n">
+        <v>57.19</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1126,6 +1236,9 @@
       <c r="E37" t="n">
         <v>0.7322513380474275</v>
       </c>
+      <c r="F37" t="n">
+        <v>66.23999999999999</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1145,6 +1258,9 @@
       <c r="E38" t="n">
         <v>13.40527698558425</v>
       </c>
+      <c r="F38" t="n">
+        <v>56.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1164,6 +1280,9 @@
       <c r="E39" t="n">
         <v>1.090272623093852</v>
       </c>
+      <c r="F39" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1183,6 +1302,9 @@
       <c r="E40" t="n">
         <v>4.049593214048521</v>
       </c>
+      <c r="F40" t="n">
+        <v>50.65</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1202,6 +1324,9 @@
       <c r="E41" t="n">
         <v>199.2925330605149</v>
       </c>
+      <c r="F41" t="n">
+        <v>28.18</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1221,6 +1346,9 @@
       <c r="E42" t="n">
         <v>0.4213848302535453</v>
       </c>
+      <c r="F42" t="n">
+        <v>62.92</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1240,6 +1368,9 @@
       <c r="E43" t="n">
         <v>0.813005837272597</v>
       </c>
+      <c r="F43" t="n">
+        <v>43.81</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1259,6 +1390,9 @@
       <c r="E44" t="n">
         <v>3.166558011355497</v>
       </c>
+      <c r="F44" t="n">
+        <v>45.73</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1278,6 +1412,9 @@
       <c r="E45" t="n">
         <v>2.006196608326496</v>
       </c>
+      <c r="F45" t="n">
+        <v>53.84</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1297,6 +1434,9 @@
       <c r="E46" t="n">
         <v>10.10245788894532</v>
       </c>
+      <c r="F46" t="n">
+        <v>60.68</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1316,6 +1456,9 @@
       <c r="E47" t="n">
         <v>0.9574583935617456</v>
       </c>
+      <c r="F47" t="n">
+        <v>51.38</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1335,6 +1478,9 @@
       <c r="E48" t="n">
         <v>0.4015395684390098</v>
       </c>
+      <c r="F48" t="n">
+        <v>52.09</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1354,6 +1500,9 @@
       <c r="E49" t="n">
         <v>1.847381610475186</v>
       </c>
+      <c r="F49" t="n">
+        <v>58.17</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1373,6 +1522,9 @@
       <c r="E50" t="n">
         <v>0.1349905913453399</v>
       </c>
+      <c r="F50" t="n">
+        <v>56.59</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1392,6 +1544,9 @@
       <c r="E51" t="n">
         <v>1.619406489692802</v>
       </c>
+      <c r="F51" t="n">
+        <v>70.34999999999999</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1411,6 +1566,9 @@
       <c r="E52" t="n">
         <v>16.87955823273561</v>
       </c>
+      <c r="F52" t="n">
+        <v>50.09</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1430,6 +1588,9 @@
       <c r="E53" t="n">
         <v>2.134680903361071</v>
       </c>
+      <c r="F53" t="n">
+        <v>68.75</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1449,6 +1610,9 @@
       <c r="E54" t="n">
         <v>0.6439166048104595</v>
       </c>
+      <c r="F54" t="n">
+        <v>60.28</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1468,6 +1632,9 @@
       <c r="E55" t="n">
         <v>0.430662447422224</v>
       </c>
+      <c r="F55" t="n">
+        <v>46.36</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1487,6 +1654,9 @@
       <c r="E56" t="n">
         <v>1.043432824159081</v>
       </c>
+      <c r="F56" t="n">
+        <v>43.98</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1506,6 +1676,9 @@
       <c r="E57" t="n">
         <v>5.106083395189541</v>
       </c>
+      <c r="F57" t="n">
+        <v>48.17</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1525,6 +1698,9 @@
       <c r="E58" t="n">
         <v>4.685022089177117</v>
       </c>
+      <c r="F58" t="n">
+        <v>48.1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1544,6 +1720,9 @@
       <c r="E59" t="n">
         <v>1.512494139938274</v>
       </c>
+      <c r="F59" t="n">
+        <v>55.53</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1563,6 +1742,9 @@
       <c r="E60" t="n">
         <v>0.659162125118829</v>
       </c>
+      <c r="F60" t="n">
+        <v>64.14</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1582,6 +1764,9 @@
       <c r="E61" t="n">
         <v>0.5060260968082197</v>
       </c>
+      <c r="F61" t="n">
+        <v>47.32</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1601,6 +1786,9 @@
       <c r="E62" t="n">
         <v>15.26864313526325</v>
       </c>
+      <c r="F62" t="n">
+        <v>47.53</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1620,6 +1808,9 @@
       <c r="E63" t="n">
         <v>5.064647875402065</v>
       </c>
+      <c r="F63" t="n">
+        <v>57.73</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1639,6 +1830,9 @@
       <c r="E64" t="n">
         <v>6.387167360107305</v>
       </c>
+      <c r="F64" t="n">
+        <v>55.46</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1658,6 +1852,9 @@
       <c r="E65" t="n">
         <v>0.3926640166165306</v>
       </c>
+      <c r="F65" t="n">
+        <v>46.68</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1677,6 +1874,9 @@
       <c r="E66" t="n">
         <v>18.6294438801422</v>
       </c>
+      <c r="F66" t="n">
+        <v>60.53</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1696,6 +1896,9 @@
       <c r="E67" t="n">
         <v>0.3069549165917881</v>
       </c>
+      <c r="F67" t="n">
+        <v>56.71</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1715,6 +1918,9 @@
       <c r="E68" t="n">
         <v>0.1696548911981873</v>
       </c>
+      <c r="F68" t="n">
+        <v>45.14</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1734,6 +1940,9 @@
       <c r="E69" t="n">
         <v>4.549423923376438</v>
       </c>
+      <c r="F69" t="n">
+        <v>43.3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1753,6 +1962,9 @@
       <c r="E70" t="n">
         <v>1.303097449570913</v>
       </c>
+      <c r="F70" t="n">
+        <v>57.74</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1772,6 +1984,9 @@
       <c r="E71" t="n">
         <v>4.877359895690901</v>
       </c>
+      <c r="F71" t="n">
+        <v>60.44</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1791,6 +2006,9 @@
       <c r="E72" t="n">
         <v>0.500464328502038</v>
       </c>
+      <c r="F72" t="n">
+        <v>60.42</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1810,6 +2028,9 @@
       <c r="E73" t="n">
         <v>1.096391911161464</v>
       </c>
+      <c r="F73" t="n">
+        <v>35.7</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1829,6 +2050,9 @@
       <c r="E74" t="n">
         <v>3.464981654751208</v>
       </c>
+      <c r="F74" t="n">
+        <v>64.31</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1848,6 +2072,9 @@
       <c r="E75" t="n">
         <v>1.023818302275006</v>
       </c>
+      <c r="F75" t="n">
+        <v>40.94</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1867,6 +2094,9 @@
       <c r="E76" t="n">
         <v>0.3535863577763019</v>
       </c>
+      <c r="F76" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1886,6 +2116,9 @@
       <c r="E77" t="n">
         <v>0.4564686942480238</v>
       </c>
+      <c r="F77" t="n">
+        <v>49.07</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1905,6 +2138,9 @@
       <c r="E78" t="n">
         <v>0.3622865146957326</v>
       </c>
+      <c r="F78" t="n">
+        <v>68.34</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1924,6 +2160,9 @@
       <c r="E79" t="n">
         <v>0.7717595486450235</v>
       </c>
+      <c r="F79" t="n">
+        <v>48.92</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1943,6 +2182,9 @@
       <c r="E80" t="n">
         <v>5.946273407691005</v>
       </c>
+      <c r="F80" t="n">
+        <v>51.59</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1962,6 +2204,9 @@
       <c r="E81" t="n">
         <v>2.943718176609238</v>
       </c>
+      <c r="F81" t="n">
+        <v>52.12</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1981,6 +2226,9 @@
       <c r="E82" t="n">
         <v>18.27177257100442</v>
       </c>
+      <c r="F82" t="n">
+        <v>58.7</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2000,6 +2248,9 @@
       <c r="E83" t="n">
         <v>0.262606864736753</v>
       </c>
+      <c r="F83" t="n">
+        <v>46.98</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2019,6 +2270,9 @@
       <c r="E84" t="n">
         <v>7.487065948483546</v>
       </c>
+      <c r="F84" t="n">
+        <v>48.61</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2038,6 +2292,9 @@
       <c r="E85" t="n">
         <v>2.122658010053261</v>
       </c>
+      <c r="F85" t="n">
+        <v>53.24</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2057,6 +2314,9 @@
       <c r="E86" t="n">
         <v>1.733405851597192</v>
       </c>
+      <c r="F86" t="n">
+        <v>50.67</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2076,6 +2336,9 @@
       <c r="E87" t="n">
         <v>0.3935059935409098</v>
       </c>
+      <c r="F87" t="n">
+        <v>39.37</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2095,6 +2358,9 @@
       <c r="E88" t="n">
         <v>0.2549570424919587</v>
       </c>
+      <c r="F88" t="n">
+        <v>54.87</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2114,6 +2380,9 @@
       <c r="E89" t="n">
         <v>7.586272724017137</v>
       </c>
+      <c r="F89" t="n">
+        <v>57.47</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2133,6 +2402,9 @@
       <c r="E90" t="n">
         <v>0.5056663541300412</v>
       </c>
+      <c r="F90" t="n">
+        <v>52.77</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2152,6 +2424,9 @@
       <c r="E91" t="n">
         <v>0.8853507409722493</v>
       </c>
+      <c r="F91" t="n">
+        <v>48.15</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2171,6 +2446,9 @@
       <c r="E92" t="n">
         <v>0.6263323501451993</v>
       </c>
+      <c r="F92" t="n">
+        <v>44.47</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2190,6 +2468,9 @@
       <c r="E93" t="n">
         <v>1.591677410113164</v>
       </c>
+      <c r="F93" t="n">
+        <v>65.14</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2209,6 +2490,9 @@
       <c r="E94" t="n">
         <v>0.6982108905991588</v>
       </c>
+      <c r="F94" t="n">
+        <v>61.08</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2228,6 +2512,9 @@
       <c r="E95" t="n">
         <v>4.126189104191898</v>
       </c>
+      <c r="F95" t="n">
+        <v>51.93</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2247,6 +2534,9 @@
       <c r="E96" t="n">
         <v>8.521357076350093</v>
       </c>
+      <c r="F96" t="n">
+        <v>46.82</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2266,6 +2556,9 @@
       <c r="E97" t="n">
         <v>4.958852192965321</v>
       </c>
+      <c r="F97" t="n">
+        <v>39.55</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2285,6 +2578,9 @@
       <c r="E98" t="n">
         <v>0.08546615163235274</v>
       </c>
+      <c r="F98" t="n">
+        <v>41.6</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2304,6 +2600,9 @@
       <c r="E99" t="n">
         <v>0.1329131180737326</v>
       </c>
+      <c r="F99" t="n">
+        <v>61.23</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2323,6 +2622,9 @@
       <c r="E100" t="n">
         <v>2.224442398848824</v>
       </c>
+      <c r="F100" t="n">
+        <v>32.1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2342,6 +2644,9 @@
       <c r="E101" t="n">
         <v>1.147662160930317</v>
       </c>
+      <c r="F101" t="n">
+        <v>42.18</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2361,6 +2666,9 @@
       <c r="E102" t="n">
         <v>13.70857058444349</v>
       </c>
+      <c r="F102" t="n">
+        <v>56.17</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2380,6 +2688,9 @@
       <c r="E103" t="n">
         <v>4.542216454402209</v>
       </c>
+      <c r="F103" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2399,6 +2710,9 @@
       <c r="E104" t="n">
         <v>0.9075355510411376</v>
       </c>
+      <c r="F104" t="n">
+        <v>50.37</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2418,6 +2732,9 @@
       <c r="E105" t="n">
         <v>0.5928518641507469</v>
       </c>
+      <c r="F105" t="n">
+        <v>65.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2437,6 +2754,9 @@
       <c r="E106" t="n">
         <v>0.4362409006263755</v>
       </c>
+      <c r="F106" t="n">
+        <v>59.59</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2456,6 +2776,9 @@
       <c r="E107" t="n">
         <v>1.66792942857887</v>
       </c>
+      <c r="F107" t="n">
+        <v>64.89</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2475,6 +2798,9 @@
       <c r="E108" t="n">
         <v>1.775672767642041</v>
       </c>
+      <c r="F108" t="n">
+        <v>49.85</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2494,6 +2820,9 @@
       <c r="E109" t="n">
         <v>12.28701931215898</v>
       </c>
+      <c r="F109" t="n">
+        <v>61.41</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2513,6 +2842,9 @@
       <c r="E110" t="n">
         <v>1</v>
       </c>
+      <c r="F110" t="n">
+        <v>56.49</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2532,6 +2864,9 @@
       <c r="E111" t="n">
         <v>4.188055891966506</v>
       </c>
+      <c r="F111" t="n">
+        <v>53.25</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2551,6 +2886,9 @@
       <c r="E112" t="n">
         <v>8.809582991496399</v>
       </c>
+      <c r="F112" t="n">
+        <v>47.63</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2570,6 +2908,9 @@
       <c r="E113" t="n">
         <v>0.7670478962378404</v>
       </c>
+      <c r="F113" t="n">
+        <v>68.89</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2589,6 +2930,9 @@
       <c r="E114" t="n">
         <v>0.741248567540467</v>
       </c>
+      <c r="F114" t="n">
+        <v>60.8</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2608,6 +2952,9 @@
       <c r="E115" t="n">
         <v>0.8089851838106028</v>
       </c>
+      <c r="F115" t="n">
+        <v>51.01</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2627,6 +2974,9 @@
       <c r="E116" t="n">
         <v>2.123780781602011</v>
       </c>
+      <c r="F116" t="n">
+        <v>63.3</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2646,6 +2996,9 @@
       <c r="E117" t="n">
         <v>0.1457792091521142</v>
       </c>
+      <c r="F117" t="n">
+        <v>49.5</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2665,6 +3018,9 @@
       <c r="E118" t="n">
         <v>0.6912081168366084</v>
       </c>
+      <c r="F118" t="n">
+        <v>53.61</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2684,6 +3040,9 @@
       <c r="E119" t="n">
         <v>4.100850441457983</v>
       </c>
+      <c r="F119" t="n">
+        <v>59.92</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2703,6 +3062,9 @@
       <c r="E120" t="n">
         <v>0.3438000546939095</v>
       </c>
+      <c r="F120" t="n">
+        <v>49.74</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2722,6 +3084,9 @@
       <c r="E121" t="n">
         <v>0.5554402534151137</v>
       </c>
+      <c r="F121" t="n">
+        <v>62.33</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2741,6 +3106,9 @@
       <c r="E122" t="n">
         <v>0.6573772479847899</v>
       </c>
+      <c r="F122" t="n">
+        <v>45.86</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2760,6 +3128,9 @@
       <c r="E123" t="n">
         <v>0.1896857216340457</v>
       </c>
+      <c r="F123" t="n">
+        <v>57.93</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2779,6 +3150,9 @@
       <c r="E124" t="n">
         <v>0.2744030876014116</v>
       </c>
+      <c r="F124" t="n">
+        <v>54.11</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2798,6 +3172,9 @@
       <c r="E125" t="n">
         <v>0.3066672038389915</v>
       </c>
+      <c r="F125" t="n">
+        <v>56.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2817,6 +3194,9 @@
       <c r="E126" t="n">
         <v>1.418633042934719</v>
       </c>
+      <c r="F126" t="n">
+        <v>56.25</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2836,6 +3216,9 @@
       <c r="E127" t="n">
         <v>0.8543038083890039</v>
       </c>
+      <c r="F127" t="n">
+        <v>48.06</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2855,6 +3238,9 @@
       <c r="E128" t="n">
         <v>0.0374873031995937</v>
       </c>
+      <c r="F128" t="n">
+        <v>53.15</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2874,6 +3260,9 @@
       <c r="E129" t="n">
         <v>1.290540232579339</v>
       </c>
+      <c r="F129" t="n">
+        <v>41.38</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2893,6 +3282,9 @@
       <c r="E130" t="n">
         <v>1.814661304710187</v>
       </c>
+      <c r="F130" t="n">
+        <v>41.76</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2912,6 +3304,9 @@
       <c r="E131" t="n">
         <v>0.4397976325350627</v>
       </c>
+      <c r="F131" t="n">
+        <v>62.62</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2931,6 +3326,9 @@
       <c r="E132" t="n">
         <v>0.4466445449336511</v>
       </c>
+      <c r="F132" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2950,6 +3348,9 @@
       <c r="E133" t="n">
         <v>1.460141813493769</v>
       </c>
+      <c r="F133" t="n">
+        <v>40.5</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2969,6 +3370,9 @@
       <c r="E134" t="n">
         <v>3.718427696605071</v>
       </c>
+      <c r="F134" t="n">
+        <v>33.56</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2988,6 +3392,9 @@
       <c r="E135" t="n">
         <v>0.08858500670651509</v>
       </c>
+      <c r="F135" t="n">
+        <v>26.29</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3007,6 +3414,9 @@
       <c r="E136" t="n">
         <v>0.3379648168405152</v>
       </c>
+      <c r="F136" t="n">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3026,6 +3436,9 @@
       <c r="E137" t="n">
         <v>0.1990776913961272</v>
       </c>
+      <c r="F137" t="n">
+        <v>55.1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3045,6 +3458,9 @@
       <c r="E138" t="n">
         <v>0.1834944036410517</v>
       </c>
+      <c r="F138" t="n">
+        <v>40.4</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3064,6 +3480,9 @@
       <c r="E139" t="n">
         <v>2.887700462944876</v>
       </c>
+      <c r="F139" t="n">
+        <v>63.33</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3083,6 +3502,9 @@
       <c r="E140" t="n">
         <v>0.7647567748824732</v>
       </c>
+      <c r="F140" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3102,6 +3524,9 @@
       <c r="E141" t="n">
         <v>0.1544187307106301</v>
       </c>
+      <c r="F141" t="n">
+        <v>57.23</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3121,6 +3546,9 @@
       <c r="E142" t="n">
         <v>1.008430756859528</v>
       </c>
+      <c r="F142" t="n">
+        <v>48.01</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3140,6 +3568,9 @@
       <c r="E143" t="n">
         <v>49.23852282494042</v>
       </c>
+      <c r="F143" t="n">
+        <v>44.37</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3159,6 +3590,9 @@
       <c r="E144" t="n">
         <v>0.2351992746545819</v>
       </c>
+      <c r="F144" t="n">
+        <v>64.53</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3178,6 +3612,9 @@
       <c r="E145" t="n">
         <v>0.4978281146228073</v>
       </c>
+      <c r="F145" t="n">
+        <v>37.69</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3197,6 +3634,9 @@
       <c r="E146" t="n">
         <v>0.9854410022007787</v>
       </c>
+      <c r="F146" t="n">
+        <v>47.23</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3216,6 +3656,9 @@
       <c r="E147" t="n">
         <v>0.9955748394994205</v>
       </c>
+      <c r="F147" t="n">
+        <v>51.96</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3235,6 +3678,9 @@
       <c r="E148" t="n">
         <v>1.342686642965973</v>
       </c>
+      <c r="F148" t="n">
+        <v>39.21</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3254,6 +3700,9 @@
       <c r="E149" t="n">
         <v>10.42461315453634</v>
       </c>
+      <c r="F149" t="n">
+        <v>51.85</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3273,6 +3722,9 @@
       <c r="E150" t="n">
         <v>0.4333556341237905</v>
       </c>
+      <c r="F150" t="n">
+        <v>60.22</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3292,6 +3744,9 @@
       <c r="E151" t="n">
         <v>4.517619659204855</v>
       </c>
+      <c r="F151" t="n">
+        <v>49.4</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3311,6 +3766,9 @@
       <c r="E152" t="n">
         <v>1.774933341797867</v>
       </c>
+      <c r="F152" t="n">
+        <v>50.04</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3330,6 +3788,9 @@
       <c r="E153" t="n">
         <v>0.4827172943443893</v>
       </c>
+      <c r="F153" t="n">
+        <v>42.81</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3349,6 +3810,9 @@
       <c r="E154" t="n">
         <v>0.3460069376619656</v>
       </c>
+      <c r="F154" t="n">
+        <v>41.78</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3368,6 +3832,9 @@
       <c r="E155" t="n">
         <v>1.146812858928781</v>
       </c>
+      <c r="F155" t="n">
+        <v>61.31</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3387,6 +3854,9 @@
       <c r="E156" t="n">
         <v>0.5658288406193435</v>
       </c>
+      <c r="F156" t="n">
+        <v>39.88</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3406,6 +3876,9 @@
       <c r="E157" t="n">
         <v>0.3269975485408446</v>
       </c>
+      <c r="F157" t="n">
+        <v>48.63</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3425,6 +3898,9 @@
       <c r="E158" t="n">
         <v>0.192874164941204</v>
       </c>
+      <c r="F158" t="n">
+        <v>45.7</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3444,6 +3920,9 @@
       <c r="E159" t="n">
         <v>0.2631208409839695</v>
       </c>
+      <c r="F159" t="n">
+        <v>62.55</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3463,6 +3942,9 @@
       <c r="E160" t="n">
         <v>1.856479356304775</v>
       </c>
+      <c r="F160" t="n">
+        <v>40.34</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3482,6 +3964,9 @@
       <c r="E161" t="n">
         <v>9.821464266645831</v>
       </c>
+      <c r="F161" t="n">
+        <v>48.04</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3501,6 +3986,9 @@
       <c r="E162" t="n">
         <v>0.2982987101353023</v>
       </c>
+      <c r="F162" t="n">
+        <v>49.84</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3520,6 +4008,9 @@
       <c r="E163" t="n">
         <v>0.0125942493260929</v>
       </c>
+      <c r="F163" t="n">
+        <v>52.17</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3539,6 +4030,9 @@
       <c r="E164" t="n">
         <v>1.332597570027738</v>
       </c>
+      <c r="F164" t="n">
+        <v>52.09</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3558,6 +4052,9 @@
       <c r="E165" t="n">
         <v>4.399241935903947</v>
       </c>
+      <c r="F165" t="n">
+        <v>53.81</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3577,6 +4074,9 @@
       <c r="E166" t="n">
         <v>0.1950810479092602</v>
       </c>
+      <c r="F166" t="n">
+        <v>62.51</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3596,6 +4096,9 @@
       <c r="E167" t="n">
         <v>0.3179942148168405</v>
       </c>
+      <c r="F167" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3615,6 +4118,9 @@
       <c r="E168" t="n">
         <v>7.545763826490083</v>
       </c>
+      <c r="F168" t="n">
+        <v>50.98</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3634,6 +4140,9 @@
       <c r="E169" t="n">
         <v>0.166015141748382</v>
       </c>
+      <c r="F169" t="n">
+        <v>39.86</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3653,6 +4162,9 @@
       <c r="E170" t="n">
         <v>8.692677608704145</v>
       </c>
+      <c r="F170" t="n">
+        <v>52.89</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3672,6 +4184,9 @@
       <c r="E171" t="n">
         <v>5.846099315023896</v>
       </c>
+      <c r="F171" t="n">
+        <v>56.16</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3691,6 +4206,9 @@
       <c r="E172" t="n">
         <v>0.5851080367490982</v>
       </c>
+      <c r="F172" t="n">
+        <v>56.23</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3710,6 +4228,9 @@
       <c r="E173" t="n">
         <v>0.3479244800823013</v>
       </c>
+      <c r="F173" t="n">
+        <v>55.02</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3729,6 +4250,9 @@
       <c r="E174" t="n">
         <v>0.5749078668073081</v>
       </c>
+      <c r="F174" t="n">
+        <v>56.28</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3748,6 +4272,9 @@
       <c r="E175" t="n">
         <v>1.025657303590265</v>
       </c>
+      <c r="F175" t="n">
+        <v>41.96</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3767,6 +4294,9 @@
       <c r="E176" t="n">
         <v>2.505892617624461</v>
       </c>
+      <c r="F176" t="n">
+        <v>28.35</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3786,6 +4316,9 @@
       <c r="E177" t="n">
         <v>6.972716529280775</v>
       </c>
+      <c r="F177" t="n">
+        <v>42.8</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3805,6 +4338,9 @@
       <c r="E178" t="n">
         <v>2.786952165618367</v>
       </c>
+      <c r="F178" t="n">
+        <v>55.33</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3824,6 +4360,9 @@
       <c r="E179" t="n">
         <v>0.0178719674180568</v>
       </c>
+      <c r="F179" t="n">
+        <v>48.89</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3843,6 +4382,9 @@
       <c r="E180" t="n">
         <v>0.1301442389082054</v>
       </c>
+      <c r="F180" t="n">
+        <v>39.09</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3862,6 +4404,9 @@
       <c r="E181" t="n">
         <v>1.544058304358584</v>
       </c>
+      <c r="F181" t="n">
+        <v>46.89</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3881,6 +4426,9 @@
       <c r="E182" t="n">
         <v>9.23683724329674</v>
       </c>
+      <c r="F182" t="n">
+        <v>33.78</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3900,6 +4448,9 @@
       <c r="E183" t="n">
         <v>0.7024065320154705</v>
       </c>
+      <c r="F183" t="n">
+        <v>43.41</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3919,6 +4470,9 @@
       <c r="E184" t="n">
         <v>1.934764083681682</v>
       </c>
+      <c r="F184" t="n">
+        <v>47.14</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3938,6 +4492,9 @@
       <c r="E185" t="n">
         <v>0.3146779896081572</v>
       </c>
+      <c r="F185" t="n">
+        <v>45.96</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3957,6 +4514,9 @@
       <c r="E186" t="n">
         <v>0.1999058320636533</v>
       </c>
+      <c r="F186" t="n">
+        <v>61.36</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3976,6 +4536,9 @@
       <c r="E187" t="n">
         <v>0.1239264692476983</v>
       </c>
+      <c r="F187" t="n">
+        <v>37.86</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3995,6 +4558,9 @@
       <c r="E188" t="n">
         <v>7.166058685262596</v>
       </c>
+      <c r="F188" t="n">
+        <v>43.06</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4014,6 +4580,9 @@
       <c r="E189" t="n">
         <v>0.2236407098488104</v>
       </c>
+      <c r="F189" t="n">
+        <v>37.16</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4033,6 +4602,9 @@
       <c r="E190" t="n">
         <v>0.8702700348999232</v>
       </c>
+      <c r="F190" t="n">
+        <v>42.44</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4052,6 +4624,9 @@
       <c r="E191" t="n">
         <v>0.1288607226107226</v>
       </c>
+      <c r="F191" t="n">
+        <v>46.02</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4071,6 +4646,9 @@
       <c r="E192" t="n">
         <v>10.92469454428253</v>
       </c>
+      <c r="F192" t="n">
+        <v>48.83</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4090,6 +4668,9 @@
       <c r="E193" t="n">
         <v>0.1245698551913636</v>
       </c>
+      <c r="F193" t="n">
+        <v>33.58</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4109,6 +4690,9 @@
       <c r="E194" t="n">
         <v>0.1841687176882708</v>
       </c>
+      <c r="F194" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4128,6 +4712,9 @@
       <c r="E195" t="n">
         <v>0.6156059954942636</v>
       </c>
+      <c r="F195" t="n">
+        <v>49.78</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4147,6 +4734,9 @@
       <c r="E196" t="n">
         <v>0.4145061758539412</v>
       </c>
+      <c r="F196" t="n">
+        <v>29.56</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4166,6 +4756,9 @@
       <c r="E197" t="n">
         <v>1.650736251644073</v>
       </c>
+      <c r="F197" t="n">
+        <v>40.44</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4185,6 +4778,9 @@
       <c r="E198" t="n">
         <v>0.12276218892839</v>
       </c>
+      <c r="F198" t="n">
+        <v>58.72</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4204,6 +4800,9 @@
       <c r="E199" t="n">
         <v>0.1753782181505645</v>
       </c>
+      <c r="F199" t="n">
+        <v>41.75</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4223,6 +4822,9 @@
       <c r="E200" t="n">
         <v>1.174180161086586</v>
       </c>
+      <c r="F200" t="n">
+        <v>28.96</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4242,6 +4844,9 @@
       <c r="E201" t="n">
         <v>0.2234974638955086</v>
       </c>
+      <c r="F201" t="n">
+        <v>25.8</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4261,6 +4866,9 @@
       <c r="E202" t="n">
         <v>0.01336297547889727</v>
       </c>
+      <c r="F202" t="n">
+        <v>40.08</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4280,6 +4888,9 @@
       <c r="E203" t="n">
         <v>0.1497555052024326</v>
       </c>
+      <c r="F203" t="n">
+        <v>50.85</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4299,6 +4910,9 @@
       <c r="E204" t="n">
         <v>0.5291717128309307</v>
       </c>
+      <c r="F204" t="n">
+        <v>41.05</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4318,6 +4932,9 @@
       <c r="E205" t="n">
         <v>0.1075598051855035</v>
       </c>
+      <c r="F205" t="n">
+        <v>44.46</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4337,6 +4954,9 @@
       <c r="E206" t="n">
         <v>0.2813118562071076</v>
       </c>
+      <c r="F206" t="n">
+        <v>58.22</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4356,6 +4976,9 @@
       <c r="E207" t="n">
         <v>1.855473785990546</v>
       </c>
+      <c r="F207" t="n">
+        <v>39.41</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4375,6 +4998,9 @@
       <c r="E208" t="n">
         <v>0.06501209451628447</v>
       </c>
+      <c r="F208" t="n">
+        <v>24.41</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4394,6 +5020,9 @@
       <c r="E209" t="n">
         <v>0.6160129442252348</v>
       </c>
+      <c r="F209" t="n">
+        <v>40.82</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4413,6 +5042,9 @@
       <c r="E210" t="n">
         <v>0.6186084632313683</v>
       </c>
+      <c r="F210" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4431,6 +5063,9 @@
       </c>
       <c r="E211" t="n">
         <v>0.05731954265473819</v>
+      </c>
+      <c r="F211" t="n">
+        <v>40.79</v>
       </c>
     </row>
     <row r="212">
@@ -4448,6 +5083,9 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
         <v>27.35854584196065</v>
+      </c>
+      <c r="F212" t="n">
+        <v>53.68</v>
       </c>
     </row>
   </sheetData>
